--- a/outputs/optimalisatie_resultaat.xlsx
+++ b/outputs/optimalisatie_resultaat.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="308">
   <si>
     <t>POSTCODE_KEY</t>
   </si>
@@ -44,403 +44,889 @@
     <t>tel nummer</t>
   </si>
   <si>
-    <t>3056KA</t>
-  </si>
-  <si>
-    <t>2629JE</t>
-  </si>
-  <si>
-    <t>3364BC</t>
-  </si>
-  <si>
-    <t>2907LE</t>
-  </si>
-  <si>
-    <t>2912EE</t>
-  </si>
-  <si>
-    <t>2391MS</t>
-  </si>
-  <si>
-    <t>2742WJ</t>
-  </si>
-  <si>
-    <t>2631PB</t>
-  </si>
-  <si>
-    <t>2153KE</t>
-  </si>
-  <si>
-    <t>3335LJ</t>
-  </si>
-  <si>
-    <t>2661CS</t>
-  </si>
-  <si>
-    <t>3238LC</t>
-  </si>
-  <si>
-    <t>3138HA</t>
-  </si>
-  <si>
-    <t>2635AC</t>
-  </si>
-  <si>
-    <t>2941LD</t>
-  </si>
-  <si>
-    <t>2544LG</t>
-  </si>
-  <si>
-    <t>2661GT</t>
-  </si>
-  <si>
-    <t>3234KR</t>
-  </si>
-  <si>
-    <t>3141EM</t>
-  </si>
-  <si>
-    <t>3062CG</t>
-  </si>
-  <si>
-    <t>2152NA</t>
-  </si>
-  <si>
-    <t>2394AD</t>
-  </si>
-  <si>
-    <t>2742JA</t>
-  </si>
-  <si>
-    <t>2165AR</t>
-  </si>
-  <si>
-    <t>2144KV</t>
-  </si>
-  <si>
-    <t>2114BC</t>
-  </si>
-  <si>
-    <t>2641NX</t>
-  </si>
-  <si>
-    <t>3329KM</t>
-  </si>
-  <si>
-    <t>3209BC</t>
-  </si>
-  <si>
-    <t>3208LR</t>
-  </si>
-  <si>
-    <t>2241BG</t>
-  </si>
-  <si>
-    <t>2223LC</t>
-  </si>
-  <si>
-    <t>2244BN</t>
-  </si>
-  <si>
-    <t>Manege De Prinsenstad Bv</t>
-  </si>
-  <si>
-    <t>Stoeterij Black Horses Bv</t>
-  </si>
-  <si>
-    <t>Capelse manege VOF</t>
-  </si>
-  <si>
-    <t>Pensionstal Parkzicht / Stoeterij Parkzicht VOF</t>
-  </si>
-  <si>
-    <t>Fa Kaptein</t>
-  </si>
-  <si>
-    <t>Stal Everse Bv</t>
-  </si>
-  <si>
-    <t>Hippisch Centrum Nootdorp</t>
-  </si>
-  <si>
-    <t>Nijssen Fourages Bv</t>
-  </si>
-  <si>
-    <t>RSV De Hoge Devel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manege Lansbergen </t>
-  </si>
-  <si>
-    <t>P De Ronde</t>
-  </si>
-  <si>
-    <t>LR &amp; PC Die Flardingha Ruiters</t>
-  </si>
-  <si>
-    <t>Manege Berestein</t>
-  </si>
-  <si>
-    <t>Horsecenter Pirouette</t>
-  </si>
-  <si>
-    <t>Manege Middenhof CV</t>
-  </si>
-  <si>
-    <t>Rotterdamsche Manege 'De Jockeyclub'</t>
-  </si>
-  <si>
-    <t>Meers Paarden Centrum</t>
-  </si>
-  <si>
-    <t>Manege Xenophon</t>
-  </si>
-  <si>
-    <t>Manege Reigersburgh</t>
-  </si>
-  <si>
-    <t>Stal Jasper</t>
-  </si>
-  <si>
-    <t>Stal S Gravenweg</t>
-  </si>
-  <si>
-    <t>HC Dordrecht</t>
-  </si>
-  <si>
-    <t>Stoeterij Willemshof</t>
-  </si>
-  <si>
-    <t>Manege De Ruiterhoek</t>
-  </si>
-  <si>
-    <t>Stoeterij Van Alle Winden Bv</t>
-  </si>
-  <si>
-    <t>Rijksstraatweg 145</t>
-  </si>
-  <si>
-    <t>Kweldamweg 8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bermweg 153 </t>
-  </si>
-  <si>
-    <t>Hoofdweg Zuid 46</t>
-  </si>
-  <si>
-    <t>Burmadeweg 12</t>
-  </si>
-  <si>
-    <t>Noordeinde 142</t>
-  </si>
-  <si>
-    <t>Oudeweg 62</t>
-  </si>
-  <si>
-    <t>Rijnlanderweg 1427</t>
-  </si>
-  <si>
-    <t>Munnikensteeg 15</t>
-  </si>
-  <si>
-    <t>Bergweg-Zuid 135</t>
-  </si>
-  <si>
-    <t>Meeldijk 1</t>
-  </si>
-  <si>
-    <t>Broekpolderweg 251</t>
-  </si>
-  <si>
-    <t>Lozerlaan 10</t>
-  </si>
-  <si>
-    <t>Bosweg 10</t>
-  </si>
-  <si>
-    <t>Zuidbuurt 8</t>
-  </si>
-  <si>
-    <t>Kralingseweg 120</t>
-  </si>
-  <si>
-    <t>Ijweg 1273</t>
-  </si>
-  <si>
-    <t>Rijndijk 79</t>
-  </si>
-  <si>
-    <t>Zevende Tochtweg 10</t>
-  </si>
-  <si>
-    <t>Hillegommerdijk 417</t>
-  </si>
-  <si>
-    <t>Vogelenzangseweg 164</t>
-  </si>
-  <si>
-    <t>Oude Veerweg 1 A</t>
-  </si>
-  <si>
-    <t>Toldijk 7 A</t>
-  </si>
-  <si>
-    <t>Breekade 9</t>
-  </si>
-  <si>
-    <t>Oostdorperweg 214</t>
-  </si>
-  <si>
-    <t>Delft</t>
-  </si>
-  <si>
-    <t>Sliedrecht</t>
-  </si>
-  <si>
-    <t>Capelle aan den IJsel</t>
-  </si>
-  <si>
-    <t>Nieuwerkerk aan den Ijsel</t>
-  </si>
-  <si>
-    <t>Hazerswoude-Dorp</t>
-  </si>
-  <si>
-    <t>Waddinxveen</t>
-  </si>
-  <si>
-    <t>Nootdorp</t>
-  </si>
-  <si>
-    <t>Nieuw-Vennep</t>
-  </si>
-  <si>
-    <t>Bergschenhoek</t>
-  </si>
-  <si>
-    <t>Zwartewaal</t>
-  </si>
-  <si>
-    <t>Den Haag</t>
-  </si>
-  <si>
-    <t>Maassluis</t>
-  </si>
-  <si>
-    <t>Hazerswoude-Rijndijk</t>
-  </si>
-  <si>
-    <t>Hoofddorp</t>
-  </si>
-  <si>
-    <t>Vogelenzang</t>
-  </si>
-  <si>
-    <t>Hekelingen</t>
-  </si>
-  <si>
-    <t>Spijkenisse</t>
-  </si>
-  <si>
-    <t>Wassenaar</t>
+    <t>3755DA</t>
+  </si>
+  <si>
+    <t>5314LN</t>
+  </si>
+  <si>
+    <t>6641KZ</t>
+  </si>
+  <si>
+    <t>47652</t>
+  </si>
+  <si>
+    <t>46569</t>
+  </si>
+  <si>
+    <t>47574</t>
+  </si>
+  <si>
+    <t>8094SB</t>
+  </si>
+  <si>
+    <t>3846AV</t>
+  </si>
+  <si>
+    <t>46539</t>
+  </si>
+  <si>
+    <t>8166KR</t>
+  </si>
+  <si>
+    <t>5306HB</t>
+  </si>
+  <si>
+    <t>3755NM</t>
+  </si>
+  <si>
+    <t>6687LD</t>
+  </si>
+  <si>
+    <t>46519</t>
+  </si>
+  <si>
+    <t>5363TM</t>
+  </si>
+  <si>
+    <t>47589</t>
+  </si>
+  <si>
+    <t>7101PA</t>
+  </si>
+  <si>
+    <t>3454HX</t>
+  </si>
+  <si>
+    <t>7274EG</t>
+  </si>
+  <si>
+    <t>7722SP</t>
+  </si>
+  <si>
+    <t>3931PX</t>
+  </si>
+  <si>
+    <t>3755MR</t>
+  </si>
+  <si>
+    <t>6741EC</t>
+  </si>
+  <si>
+    <t>46414</t>
+  </si>
+  <si>
+    <t>46485</t>
+  </si>
+  <si>
+    <t>7683AZ</t>
+  </si>
+  <si>
+    <t>46509</t>
+  </si>
+  <si>
+    <t>47665</t>
+  </si>
+  <si>
+    <t>3751LD</t>
+  </si>
+  <si>
+    <t>3584CL</t>
+  </si>
+  <si>
+    <t>7245VW</t>
+  </si>
+  <si>
+    <t>3762LB</t>
+  </si>
+  <si>
+    <t>47509</t>
+  </si>
+  <si>
+    <t>8276BC</t>
+  </si>
+  <si>
+    <t>3833AA</t>
+  </si>
+  <si>
+    <t>6718NG</t>
+  </si>
+  <si>
+    <t>6874BT</t>
+  </si>
+  <si>
+    <t>47495</t>
+  </si>
+  <si>
+    <t>3992LX</t>
+  </si>
+  <si>
+    <t>3897LT</t>
+  </si>
+  <si>
+    <t>5691PD</t>
+  </si>
+  <si>
+    <t>5855AV</t>
+  </si>
+  <si>
+    <t>47647</t>
+  </si>
+  <si>
+    <t>3862PZ</t>
+  </si>
+  <si>
+    <t>6865NA</t>
+  </si>
+  <si>
+    <t>4214KW</t>
+  </si>
+  <si>
+    <t>5866BR</t>
+  </si>
+  <si>
+    <t>47506</t>
+  </si>
+  <si>
+    <t>4105LE</t>
+  </si>
+  <si>
+    <t>3781NN</t>
+  </si>
+  <si>
+    <t>1338GA</t>
+  </si>
+  <si>
+    <t>46325</t>
+  </si>
+  <si>
+    <t>7475RV</t>
+  </si>
+  <si>
+    <t>1231KR</t>
+  </si>
+  <si>
+    <t>8251PB</t>
+  </si>
+  <si>
+    <t>5721PD</t>
+  </si>
+  <si>
+    <t>8102SL</t>
+  </si>
+  <si>
+    <t>8106AG</t>
+  </si>
+  <si>
+    <t>5725RG</t>
+  </si>
+  <si>
+    <t>5845EJ</t>
+  </si>
+  <si>
+    <t>5346JN</t>
+  </si>
+  <si>
+    <t>5425RD</t>
+  </si>
+  <si>
+    <t>5473KG</t>
+  </si>
+  <si>
+    <t>7151HA</t>
+  </si>
+  <si>
+    <t>3941PT</t>
+  </si>
+  <si>
+    <t>8219PE</t>
+  </si>
+  <si>
+    <t>5335LB</t>
+  </si>
+  <si>
+    <t>47661</t>
+  </si>
+  <si>
+    <t>6718SH</t>
+  </si>
+  <si>
+    <t>5613ES</t>
+  </si>
+  <si>
+    <t>5151RH</t>
+  </si>
+  <si>
+    <t>47625</t>
+  </si>
+  <si>
+    <t>5481XN</t>
+  </si>
+  <si>
+    <t>3896LT</t>
+  </si>
+  <si>
+    <t>6909BL</t>
+  </si>
+  <si>
+    <t>8131TC</t>
+  </si>
+  <si>
+    <t>47624</t>
+  </si>
+  <si>
+    <t>3737MN</t>
+  </si>
+  <si>
+    <t>5731PT</t>
+  </si>
+  <si>
+    <t>6718PG</t>
+  </si>
+  <si>
+    <t>7244NA</t>
+  </si>
+  <si>
+    <t>5271VC</t>
+  </si>
+  <si>
+    <t>3723MC</t>
+  </si>
+  <si>
+    <t>1213RM</t>
+  </si>
+  <si>
+    <t>6741HP</t>
+  </si>
+  <si>
+    <t>6615AK</t>
+  </si>
+  <si>
+    <t>5321JE</t>
+  </si>
+  <si>
+    <t>3766AD</t>
+  </si>
+  <si>
+    <t>6741KP</t>
+  </si>
+  <si>
+    <t>5268LE</t>
+  </si>
+  <si>
+    <t>6595MB</t>
+  </si>
+  <si>
+    <t>6624KJ</t>
+  </si>
+  <si>
+    <t>46446</t>
+  </si>
+  <si>
+    <t>7274EM</t>
+  </si>
+  <si>
+    <t>6911KM</t>
+  </si>
+  <si>
+    <t>5324AZ</t>
+  </si>
+  <si>
+    <t>5384RB</t>
+  </si>
+  <si>
+    <t>7461PN</t>
+  </si>
+  <si>
+    <t>3737BL</t>
+  </si>
+  <si>
+    <t>6661NR</t>
+  </si>
+  <si>
+    <t>6603KT</t>
+  </si>
+  <si>
+    <t>3999NR</t>
+  </si>
+  <si>
+    <t>Pensionstal De Paardenstek</t>
+  </si>
+  <si>
+    <t>Vof De Lindehoeve</t>
+  </si>
+  <si>
+    <t>Dressuurstal Van Baalen Bv</t>
+  </si>
+  <si>
+    <t>Vof Stal Paardenvreugd</t>
+  </si>
+  <si>
+    <t>Paardenopfokbedrijf Wim Ten Pas</t>
+  </si>
+  <si>
+    <t>Team Nijhof</t>
+  </si>
+  <si>
+    <t>Stal De Ontginning</t>
+  </si>
+  <si>
+    <t>Manege Groenewoude</t>
+  </si>
+  <si>
+    <t>De Nieuwe Heuvel Bv</t>
+  </si>
+  <si>
+    <t>Fred Van Straaten Sport Stables</t>
+  </si>
+  <si>
+    <t>Stal Groenendaal BV</t>
+  </si>
+  <si>
+    <t>Mvh Ruitersport</t>
+  </si>
+  <si>
+    <t>Training en Handelstal Johan Laseur B.V.</t>
+  </si>
+  <si>
+    <t>Pensionstal Klein Heiligenberg Vof</t>
+  </si>
+  <si>
+    <t>Stoeterij Van Kleef Bv</t>
+  </si>
+  <si>
+    <t>Manege En Hengstenhouderij Zilfia Bv</t>
+  </si>
+  <si>
+    <t>Sonniushof Sport Bv</t>
+  </si>
+  <si>
+    <t>Stal Van Laar</t>
+  </si>
+  <si>
+    <t>Opfokstal De Roosahoeve</t>
+  </si>
+  <si>
+    <t>Aniekpoelshorses Bv</t>
+  </si>
+  <si>
+    <t>Gh De Leeuw</t>
+  </si>
+  <si>
+    <t>Stal Jacobs</t>
+  </si>
+  <si>
+    <t>Jjs Winterstalling Opfok</t>
+  </si>
+  <si>
+    <t>Elzenburg Oss Bv</t>
+  </si>
+  <si>
+    <t>Manege Van Erp Vof</t>
+  </si>
+  <si>
+    <t>Springstal Van De Wetering</t>
+  </si>
+  <si>
+    <t>Paardenhouderij Tizzum</t>
+  </si>
+  <si>
+    <t>Lhbm Beusink</t>
+  </si>
+  <si>
+    <t>Firma Maat</t>
+  </si>
+  <si>
+    <t>Aike Wolfs</t>
+  </si>
+  <si>
+    <t>Dutchsportponys</t>
+  </si>
+  <si>
+    <t>Oscarhoeve</t>
+  </si>
+  <si>
+    <t>Jr Stables</t>
+  </si>
+  <si>
+    <t>R Vissers Drunen</t>
+  </si>
+  <si>
+    <t>Stal Witte Bv</t>
+  </si>
+  <si>
+    <t>Demro Stables Bv</t>
+  </si>
+  <si>
+    <t>Hengstenstation Gebr Van Manen Bv</t>
+  </si>
+  <si>
+    <t>Stal Felicia</t>
+  </si>
+  <si>
+    <t>Stal Beiten</t>
+  </si>
+  <si>
+    <t>Nieuw Eldorado</t>
+  </si>
+  <si>
+    <t>Kabeko Doors</t>
+  </si>
+  <si>
+    <t>Hengstenstation Van Uytert Bv</t>
+  </si>
+  <si>
+    <t>Mam Bouwmanwgpm Bouwman Peek</t>
+  </si>
+  <si>
+    <t>Stal De Fliere Fluiter</t>
+  </si>
+  <si>
+    <t>Stal Van Brenk Bv</t>
+  </si>
+  <si>
+    <t>RSC Sint Frans</t>
+  </si>
+  <si>
+    <t>Wakkerendijk 31</t>
+  </si>
+  <si>
+    <t>Nijbroekerweg 11</t>
+  </si>
+  <si>
+    <t>Verdrietweg 2</t>
+  </si>
+  <si>
+    <t>Geerenweg 10</t>
+  </si>
+  <si>
+    <t>Bataafseweg 8</t>
+  </si>
+  <si>
+    <t>Kulsdom 9</t>
+  </si>
+  <si>
+    <t>Hessenweg 40</t>
+  </si>
+  <si>
+    <t>Ekris 38</t>
+  </si>
+  <si>
+    <t>Veenstraat 1</t>
+  </si>
+  <si>
+    <t>Ommerweg 74</t>
+  </si>
+  <si>
+    <t>Zevenhuizerstraat 154</t>
+  </si>
+  <si>
+    <t>Verwoldseweg 29</t>
+  </si>
+  <si>
+    <t>Jachthuislaan 57</t>
+  </si>
+  <si>
+    <t>Ursulineweg 1</t>
+  </si>
+  <si>
+    <t>Maanderdijk 28</t>
+  </si>
+  <si>
+    <t>Fortweg 13</t>
+  </si>
+  <si>
+    <t>Sonniuswijk 35</t>
+  </si>
+  <si>
+    <t>Voorthuizerweg 2</t>
+  </si>
+  <si>
+    <t>Molenweg 3</t>
+  </si>
+  <si>
+    <t>Donkstraat 11</t>
+  </si>
+  <si>
+    <t>Prijsseweg 22</t>
+  </si>
+  <si>
+    <t>Hunnenweg 40 A</t>
+  </si>
+  <si>
+    <t>Hagweg 9</t>
+  </si>
+  <si>
+    <t>Meijelseweg 73</t>
+  </si>
+  <si>
+    <t>Frankenbeemdweg 39</t>
+  </si>
+  <si>
+    <t>Breemhorstsedijk 65</t>
+  </si>
+  <si>
+    <t>Lange Kruisdelstraat 5 c</t>
+  </si>
+  <si>
+    <t>Molenweg 20</t>
+  </si>
+  <si>
+    <t>Molenweg 9</t>
+  </si>
+  <si>
+    <t>Bijlweg 4</t>
+  </si>
+  <si>
+    <t>Veerweg 1 b</t>
+  </si>
+  <si>
+    <t>Deelweg 20</t>
+  </si>
+  <si>
+    <t>Lakerstraat 32</t>
+  </si>
+  <si>
+    <t>Margrietweg 1</t>
+  </si>
+  <si>
+    <t>Olieeindsestraat 8</t>
+  </si>
+  <si>
+    <t>Heezerweg 7</t>
+  </si>
+  <si>
+    <t>Zuiderkade 41</t>
+  </si>
+  <si>
+    <t>Lookertstraat 8</t>
+  </si>
+  <si>
+    <t>Meulunterseweg 66</t>
+  </si>
+  <si>
+    <t>Bosstraat 81</t>
+  </si>
+  <si>
+    <t>Immenweg 12</t>
+  </si>
+  <si>
+    <t>van Heemstraweg 6</t>
+  </si>
+  <si>
+    <t>de Berghoofdseweg 4</t>
+  </si>
+  <si>
+    <t>Wijststraat 16</t>
+  </si>
+  <si>
+    <t>Voordorpsedijk 29</t>
+  </si>
+  <si>
+    <t>Heumenseweg 192</t>
+  </si>
+  <si>
+    <t>Emst</t>
+  </si>
+  <si>
+    <t>Brakel</t>
+  </si>
+  <si>
+    <t>Eemnes</t>
+  </si>
+  <si>
+    <t>Winterswijk</t>
+  </si>
+  <si>
+    <t>Geesteren</t>
+  </si>
+  <si>
+    <t>Dalfsen</t>
+  </si>
+  <si>
+    <t>Lunteren</t>
+  </si>
+  <si>
+    <t>Den Ham</t>
+  </si>
+  <si>
+    <t>Laren</t>
+  </si>
+  <si>
+    <t>Leusden</t>
+  </si>
+  <si>
+    <t>Ede</t>
+  </si>
+  <si>
+    <t>Houten</t>
+  </si>
+  <si>
+    <t>Son en Breugel</t>
+  </si>
+  <si>
+    <t>Nijkerk</t>
+  </si>
+  <si>
+    <t>Vuren</t>
+  </si>
+  <si>
+    <t>Swolgen</t>
+  </si>
+  <si>
+    <t>Culemborg</t>
+  </si>
+  <si>
+    <t>Voorthuizen</t>
+  </si>
+  <si>
+    <t>Raalte</t>
+  </si>
+  <si>
+    <t>Heusden</t>
+  </si>
+  <si>
+    <t>Oss</t>
+  </si>
+  <si>
+    <t>De Mortel</t>
+  </si>
+  <si>
+    <t>Heeswijk-Dinther</t>
+  </si>
+  <si>
+    <t>Eibergen</t>
+  </si>
+  <si>
+    <t>Doorn</t>
+  </si>
+  <si>
+    <t>Lelystad</t>
+  </si>
+  <si>
+    <t>Alem</t>
+  </si>
+  <si>
+    <t>Eindhoven</t>
+  </si>
+  <si>
+    <t>Drunen</t>
+  </si>
+  <si>
+    <t>Schijndel</t>
+  </si>
+  <si>
+    <t>Mierlo</t>
+  </si>
+  <si>
+    <t>Sint-Michielsgestel</t>
+  </si>
+  <si>
+    <t>Heerewaarden</t>
+  </si>
+  <si>
+    <t>Pannerden</t>
+  </si>
+  <si>
+    <t>Heesch</t>
+  </si>
+  <si>
+    <t>Groenekan</t>
   </si>
   <si>
     <t>nan</t>
   </si>
   <si>
-    <t>27219574</t>
-  </si>
-  <si>
-    <t>54105889</t>
-  </si>
-  <si>
-    <t>28025353</t>
-  </si>
-  <si>
-    <t>24341584</t>
-  </si>
-  <si>
-    <t>24198953</t>
-  </si>
-  <si>
-    <t>28042721</t>
-  </si>
-  <si>
-    <t>69644616</t>
-  </si>
-  <si>
-    <t>53624637</t>
-  </si>
-  <si>
-    <t>74032283</t>
-  </si>
-  <si>
-    <t>010 470 4860</t>
-  </si>
-  <si>
-    <t>0184 208 520</t>
-  </si>
-  <si>
-    <t>010 450 6350</t>
-  </si>
-  <si>
-    <t>0180 321 940</t>
-  </si>
-  <si>
-    <t>071 341 3586</t>
-  </si>
-  <si>
-    <t>0252 674 041</t>
-  </si>
-  <si>
-    <t>078-6100813</t>
-  </si>
-  <si>
-    <t>010 524 0504</t>
-  </si>
-  <si>
-    <t>0181 665 077</t>
-  </si>
-  <si>
-    <t>010-4748425</t>
-  </si>
-  <si>
-    <t>070 367 6090</t>
-  </si>
-  <si>
-    <t>010 521 9399</t>
-  </si>
-  <si>
-    <t>010 592 0455</t>
-  </si>
-  <si>
-    <t>010-7200724</t>
-  </si>
-  <si>
-    <t>0252 234 325</t>
-  </si>
-  <si>
-    <t>06 22888138</t>
-  </si>
-  <si>
-    <t>0182 612 423</t>
-  </si>
-  <si>
-    <t>0252 524 898</t>
-  </si>
-  <si>
-    <t>023 584 5111</t>
-  </si>
-  <si>
-    <t>786181456</t>
-  </si>
-  <si>
-    <t>0181 687 236</t>
-  </si>
-  <si>
-    <t>0181 625 752</t>
+    <t>55291341</t>
+  </si>
+  <si>
+    <t>70556903</t>
+  </si>
+  <si>
+    <t>32164734</t>
+  </si>
+  <si>
+    <t>69709017</t>
+  </si>
+  <si>
+    <t>76925595</t>
+  </si>
+  <si>
+    <t>65353560</t>
+  </si>
+  <si>
+    <t>9153721</t>
+  </si>
+  <si>
+    <t>63446030</t>
+  </si>
+  <si>
+    <t>76671992</t>
+  </si>
+  <si>
+    <t>53657462</t>
+  </si>
+  <si>
+    <t>70072876</t>
+  </si>
+  <si>
+    <t>30053490</t>
+  </si>
+  <si>
+    <t>50208012</t>
+  </si>
+  <si>
+    <t>32079020</t>
+  </si>
+  <si>
+    <t>75831112</t>
+  </si>
+  <si>
+    <t>63904810</t>
+  </si>
+  <si>
+    <t>30269767</t>
+  </si>
+  <si>
+    <t>8195043</t>
+  </si>
+  <si>
+    <t>5073786</t>
+  </si>
+  <si>
+    <t>17131559</t>
+  </si>
+  <si>
+    <t>16056989</t>
+  </si>
+  <si>
+    <t>17168352</t>
+  </si>
+  <si>
+    <t>69929602</t>
+  </si>
+  <si>
+    <t>9213870</t>
+  </si>
+  <si>
+    <t>33207363</t>
+  </si>
+  <si>
+    <t>39071088</t>
+  </si>
+  <si>
+    <t>66265193</t>
+  </si>
+  <si>
+    <t>9137189</t>
+  </si>
+  <si>
+    <t>55069665</t>
+  </si>
+  <si>
+    <t>17270867</t>
+  </si>
+  <si>
+    <t>16043191</t>
+  </si>
+  <si>
+    <t>12056954</t>
+  </si>
+  <si>
+    <t>72005335</t>
+  </si>
+  <si>
+    <t>16039972</t>
+  </si>
+  <si>
+    <t>78101441</t>
+  </si>
+  <si>
+    <t>8225399</t>
+  </si>
+  <si>
+    <t>56863632</t>
+  </si>
+  <si>
+    <t>9211980</t>
+  </si>
+  <si>
+    <t>17245420</t>
+  </si>
+  <si>
+    <t>74470132</t>
+  </si>
+  <si>
+    <t>035-5314656</t>
+  </si>
+  <si>
+    <t>0418 674 042</t>
+  </si>
+  <si>
+    <t>06 20482281</t>
+  </si>
+  <si>
+    <t>0529-471264</t>
+  </si>
+  <si>
+    <t>033-2861456</t>
+  </si>
+  <si>
+    <t>033-4564429</t>
+  </si>
+  <si>
+    <t>088- 02 24 300</t>
+  </si>
+  <si>
+    <t>06 51921782</t>
+  </si>
+  <si>
+    <t>030 637 1325</t>
+  </si>
+  <si>
+    <t>0499 472 133</t>
+  </si>
+  <si>
+    <t>06 29044423</t>
+  </si>
+  <si>
+    <t>0345 535 700</t>
+  </si>
+  <si>
+    <t>06 16134328</t>
+  </si>
+  <si>
+    <t>0412 636 602</t>
+  </si>
+  <si>
+    <t>06 53842131</t>
+  </si>
+  <si>
+    <t>06 20515697</t>
+  </si>
+  <si>
+    <t>0343 522 002</t>
+  </si>
+  <si>
+    <t>06 29414477</t>
+  </si>
+  <si>
+    <t>073 547 5928</t>
+  </si>
+  <si>
+    <t>06 55130055</t>
+  </si>
+  <si>
+    <t>035-6018803</t>
+  </si>
+  <si>
+    <t>0412 451 350</t>
+  </si>
+  <si>
+    <t>030 272 3755</t>
+  </si>
+  <si>
+    <t>024-6412218</t>
   </si>
   <si>
     <t>Target_tons_per_year</t>
@@ -810,7 +1296,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -847,19 +1333,25 @@
         <v>9</v>
       </c>
       <c r="B2">
-        <v>8026.63</v>
+        <v>26110.3</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>14.8</v>
+        <v>60.4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F2" t="s">
+        <v>157</v>
       </c>
       <c r="H2" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
       <c r="I2" t="s">
-        <v>110</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -867,28 +1359,19 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>3472.7</v>
+        <v>16478.43</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>4.6</v>
-      </c>
-      <c r="E3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G3" t="s">
-        <v>92</v>
+        <v>56.9</v>
       </c>
       <c r="H3" t="s">
-        <v>111</v>
+        <v>239</v>
       </c>
       <c r="I3" t="s">
-        <v>120</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -896,28 +1379,19 @@
         <v>11</v>
       </c>
       <c r="B4">
-        <v>2946.12</v>
+        <v>16462.9</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>37.2</v>
-      </c>
-      <c r="E4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G4" t="s">
-        <v>93</v>
+        <v>20.6</v>
       </c>
       <c r="H4" t="s">
-        <v>112</v>
+        <v>239</v>
       </c>
       <c r="I4" t="s">
-        <v>121</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -925,28 +1399,19 @@
         <v>12</v>
       </c>
       <c r="B5">
-        <v>2424.7</v>
+        <v>5976.7</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>19.1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G5" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
       <c r="I5" t="s">
-        <v>122</v>
+        <v>239</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -954,28 +1419,19 @@
         <v>13</v>
       </c>
       <c r="B6">
-        <v>2352</v>
+        <v>4735.7</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>20.2</v>
-      </c>
-      <c r="E6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" t="s">
-        <v>70</v>
-      </c>
-      <c r="G6" t="s">
-        <v>95</v>
+        <v>63.7</v>
       </c>
       <c r="H6" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
       <c r="I6" t="s">
-        <v>123</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -983,28 +1439,19 @@
         <v>14</v>
       </c>
       <c r="B7">
-        <v>2270</v>
+        <v>3602</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>22.1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" t="s">
-        <v>71</v>
-      </c>
-      <c r="G7" t="s">
-        <v>96</v>
+        <v>33.7</v>
       </c>
       <c r="H7" t="s">
-        <v>113</v>
+        <v>239</v>
       </c>
       <c r="I7" t="s">
-        <v>124</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1012,28 +1459,19 @@
         <v>15</v>
       </c>
       <c r="B8">
-        <v>2244.02</v>
+        <v>3546.99</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>22</v>
-      </c>
-      <c r="E8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" t="s">
-        <v>72</v>
-      </c>
-      <c r="G8" t="s">
-        <v>97</v>
+        <v>56.3</v>
       </c>
       <c r="H8" t="s">
-        <v>114</v>
+        <v>239</v>
       </c>
       <c r="I8" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1041,28 +1479,19 @@
         <v>16</v>
       </c>
       <c r="B9">
-        <v>1812</v>
+        <v>3363.22</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9">
-        <v>6.1</v>
-      </c>
-      <c r="E9" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" t="s">
-        <v>73</v>
-      </c>
-      <c r="G9" t="s">
-        <v>98</v>
+        <v>50.6</v>
       </c>
       <c r="H9" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
       <c r="I9" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1070,28 +1499,19 @@
         <v>17</v>
       </c>
       <c r="B10">
-        <v>1767.94</v>
+        <v>3239.5</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>35</v>
-      </c>
-      <c r="E10" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G10" t="s">
-        <v>99</v>
+        <v>68.2</v>
       </c>
       <c r="H10" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
       <c r="I10" t="s">
-        <v>125</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1099,25 +1519,28 @@
         <v>18</v>
       </c>
       <c r="B11">
-        <v>1670.6</v>
+        <v>3208.28</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>29.1</v>
+        <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>50</v>
+        <v>112</v>
       </c>
       <c r="F11" t="s">
-        <v>75</v>
+        <v>158</v>
+      </c>
+      <c r="G11" t="s">
+        <v>203</v>
       </c>
       <c r="H11" t="s">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="I11" t="s">
-        <v>126</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1125,28 +1548,28 @@
         <v>19</v>
       </c>
       <c r="B12">
-        <v>1654.9</v>
+        <v>2755.21</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>12.7</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="E12" t="s">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="F12" t="s">
-        <v>76</v>
+        <v>159</v>
       </c>
       <c r="G12" t="s">
-        <v>100</v>
+        <v>204</v>
       </c>
       <c r="H12" t="s">
-        <v>110</v>
+        <v>241</v>
       </c>
       <c r="I12" t="s">
-        <v>127</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1154,28 +1577,28 @@
         <v>20</v>
       </c>
       <c r="B13">
-        <v>1645.3</v>
+        <v>2540.1</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13">
-        <v>16</v>
+        <v>60.4</v>
       </c>
       <c r="E13" t="s">
-        <v>52</v>
+        <v>114</v>
       </c>
       <c r="F13" t="s">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="G13" t="s">
-        <v>101</v>
+        <v>205</v>
       </c>
       <c r="H13" t="s">
-        <v>115</v>
+        <v>242</v>
       </c>
       <c r="I13" t="s">
-        <v>128</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1183,25 +1606,19 @@
         <v>21</v>
       </c>
       <c r="B14">
-        <v>1643</v>
+        <v>2506.3</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="E14" t="s">
-        <v>53</v>
-      </c>
-      <c r="F14" t="s">
-        <v>78</v>
+        <v>7.1</v>
       </c>
       <c r="H14" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
       <c r="I14" t="s">
-        <v>129</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1209,19 +1626,19 @@
         <v>22</v>
       </c>
       <c r="B15">
-        <v>1639</v>
+        <v>2221</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>1.2</v>
+        <v>55.1</v>
       </c>
       <c r="H15" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
       <c r="I15" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1229,19 +1646,19 @@
         <v>23</v>
       </c>
       <c r="B16">
-        <v>1608.1</v>
+        <v>2175.8</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16">
-        <v>27.8</v>
+        <v>31.5</v>
       </c>
       <c r="H16" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
       <c r="I16" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1249,28 +1666,19 @@
         <v>24</v>
       </c>
       <c r="B17">
-        <v>1588.7</v>
+        <v>2127.6</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17">
-        <v>5.7</v>
-      </c>
-      <c r="E17" t="s">
-        <v>54</v>
-      </c>
-      <c r="F17" t="s">
-        <v>79</v>
-      </c>
-      <c r="G17" t="s">
-        <v>102</v>
+        <v>38.1</v>
       </c>
       <c r="H17" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
       <c r="I17" t="s">
-        <v>130</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1278,28 +1686,28 @@
         <v>25</v>
       </c>
       <c r="B18">
-        <v>1507.8</v>
+        <v>1992.94</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18">
-        <v>12.7</v>
+        <v>48.7</v>
       </c>
       <c r="E18" t="s">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="F18" t="s">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="G18" t="s">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="H18" t="s">
-        <v>110</v>
+        <v>243</v>
       </c>
       <c r="I18" t="s">
-        <v>131</v>
+        <v>239</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1307,19 +1715,19 @@
         <v>26</v>
       </c>
       <c r="B19">
-        <v>1449.8</v>
+        <v>1948</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19">
-        <v>18.4</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="H19" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
       <c r="I19" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1327,28 +1735,28 @@
         <v>27</v>
       </c>
       <c r="B20">
-        <v>1391.6</v>
+        <v>1883.2</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20">
-        <v>11.1</v>
+        <v>39.7</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="F20" t="s">
-        <v>81</v>
+        <v>162</v>
       </c>
       <c r="G20" t="s">
-        <v>103</v>
+        <v>207</v>
       </c>
       <c r="H20" t="s">
-        <v>110</v>
+        <v>244</v>
       </c>
       <c r="I20" t="s">
-        <v>132</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1356,25 +1764,28 @@
         <v>28</v>
       </c>
       <c r="B21">
-        <v>1369.26</v>
+        <v>1869.7</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21">
-        <v>17</v>
+        <v>63.3</v>
       </c>
       <c r="E21" t="s">
-        <v>57</v>
+        <v>117</v>
       </c>
       <c r="F21" t="s">
-        <v>82</v>
+        <v>163</v>
+      </c>
+      <c r="G21" t="s">
+        <v>208</v>
       </c>
       <c r="H21" t="s">
-        <v>110</v>
+        <v>245</v>
       </c>
       <c r="I21" t="s">
-        <v>133</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1382,28 +1793,25 @@
         <v>29</v>
       </c>
       <c r="B22">
-        <v>1360.52</v>
+        <v>1840.9</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22">
-        <v>35.8</v>
+        <v>42.3</v>
       </c>
       <c r="E22" t="s">
-        <v>58</v>
+        <v>118</v>
       </c>
       <c r="F22" t="s">
-        <v>83</v>
-      </c>
-      <c r="G22" t="s">
-        <v>99</v>
+        <v>164</v>
       </c>
       <c r="H22" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
       <c r="I22" t="s">
-        <v>134</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1411,28 +1819,19 @@
         <v>30</v>
       </c>
       <c r="B23">
-        <v>1343</v>
+        <v>1822</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>22.1</v>
-      </c>
-      <c r="E23" t="s">
-        <v>59</v>
-      </c>
-      <c r="F23" t="s">
-        <v>84</v>
-      </c>
-      <c r="G23" t="s">
-        <v>104</v>
+        <v>60.4</v>
       </c>
       <c r="H23" t="s">
-        <v>116</v>
+        <v>239</v>
       </c>
       <c r="I23" t="s">
-        <v>135</v>
+        <v>239</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1440,28 +1839,28 @@
         <v>31</v>
       </c>
       <c r="B24">
-        <v>1319</v>
+        <v>1805.94</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24">
-        <v>22</v>
+        <v>29.9</v>
       </c>
       <c r="E24" t="s">
-        <v>60</v>
+        <v>119</v>
       </c>
       <c r="F24" t="s">
-        <v>85</v>
+        <v>165</v>
       </c>
       <c r="G24" t="s">
-        <v>97</v>
+        <v>209</v>
       </c>
       <c r="H24" t="s">
-        <v>110</v>
+        <v>246</v>
       </c>
       <c r="I24" t="s">
-        <v>136</v>
+        <v>239</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1469,19 +1868,19 @@
         <v>32</v>
       </c>
       <c r="B25">
-        <v>1304</v>
+        <v>1759.1</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25">
-        <v>32</v>
+        <v>49.2</v>
       </c>
       <c r="H25" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
       <c r="I25" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1489,28 +1888,19 @@
         <v>33</v>
       </c>
       <c r="B26">
-        <v>1239.6</v>
+        <v>1696.9</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26">
-        <v>35.7</v>
-      </c>
-      <c r="E26" t="s">
-        <v>61</v>
-      </c>
-      <c r="F26" t="s">
-        <v>86</v>
-      </c>
-      <c r="G26" t="s">
-        <v>105</v>
+        <v>57.1</v>
       </c>
       <c r="H26" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
       <c r="I26" t="s">
-        <v>137</v>
+        <v>239</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1518,28 +1908,28 @@
         <v>34</v>
       </c>
       <c r="B27">
-        <v>1235.8</v>
+        <v>1624.9</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27">
-        <v>38.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="E27" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="F27" t="s">
-        <v>87</v>
+        <v>166</v>
       </c>
       <c r="G27" t="s">
-        <v>106</v>
+        <v>210</v>
       </c>
       <c r="H27" t="s">
-        <v>117</v>
+        <v>247</v>
       </c>
       <c r="I27" t="s">
-        <v>138</v>
+        <v>239</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1547,19 +1937,19 @@
         <v>35</v>
       </c>
       <c r="B28">
-        <v>1234</v>
+        <v>1535.6</v>
       </c>
       <c r="C28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28">
-        <v>7.7</v>
+        <v>45.8</v>
       </c>
       <c r="H28" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
       <c r="I28" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1567,25 +1957,19 @@
         <v>36</v>
       </c>
       <c r="B29">
-        <v>1200.5</v>
+        <v>1517.4</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
       <c r="D29">
-        <v>36.9</v>
-      </c>
-      <c r="E29" t="s">
-        <v>63</v>
-      </c>
-      <c r="F29" t="s">
-        <v>88</v>
+        <v>47.4</v>
       </c>
       <c r="H29" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
       <c r="I29" t="s">
-        <v>139</v>
+        <v>239</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1593,28 +1977,25 @@
         <v>37</v>
       </c>
       <c r="B30">
-        <v>1186.6</v>
+        <v>1505.9</v>
       </c>
       <c r="C30">
         <v>1</v>
       </c>
       <c r="D30">
-        <v>20.9</v>
+        <v>52.9</v>
       </c>
       <c r="E30" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="F30" t="s">
-        <v>89</v>
-      </c>
-      <c r="G30" t="s">
-        <v>107</v>
+        <v>167</v>
       </c>
       <c r="H30" t="s">
-        <v>118</v>
+        <v>239</v>
       </c>
       <c r="I30" t="s">
-        <v>140</v>
+        <v>285</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1622,28 +2003,19 @@
         <v>38</v>
       </c>
       <c r="B31">
-        <v>1169.8</v>
+        <v>1473.8</v>
       </c>
       <c r="C31">
         <v>1</v>
       </c>
       <c r="D31">
-        <v>19.6</v>
-      </c>
-      <c r="E31" t="s">
-        <v>65</v>
-      </c>
-      <c r="F31" t="s">
-        <v>90</v>
-      </c>
-      <c r="G31" t="s">
-        <v>108</v>
+        <v>59.4</v>
       </c>
       <c r="H31" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
       <c r="I31" t="s">
-        <v>141</v>
+        <v>239</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1651,28 +2023,28 @@
         <v>39</v>
       </c>
       <c r="B32">
-        <v>1162.3</v>
+        <v>1452.3</v>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D32">
-        <v>16.1</v>
+        <v>35.5</v>
       </c>
       <c r="E32" t="s">
-        <v>66</v>
+        <v>122</v>
       </c>
       <c r="F32" t="s">
-        <v>91</v>
+        <v>168</v>
       </c>
       <c r="G32" t="s">
-        <v>109</v>
+        <v>211</v>
       </c>
       <c r="H32" t="s">
-        <v>119</v>
+        <v>248</v>
       </c>
       <c r="I32" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1680,19 +2052,25 @@
         <v>40</v>
       </c>
       <c r="B33">
-        <v>1099.9</v>
+        <v>1442.7</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33">
-        <v>21</v>
+        <v>55.2</v>
+      </c>
+      <c r="E33" t="s">
+        <v>123</v>
+      </c>
+      <c r="F33" t="s">
+        <v>169</v>
       </c>
       <c r="H33" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
       <c r="I33" t="s">
-        <v>110</v>
+        <v>286</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1700,19 +2078,1690 @@
         <v>41</v>
       </c>
       <c r="B34">
-        <v>1074.72</v>
+        <v>1400.9</v>
       </c>
       <c r="C34">
         <v>1</v>
       </c>
       <c r="D34">
-        <v>11.2</v>
+        <v>63.9</v>
       </c>
       <c r="H34" t="s">
+        <v>239</v>
+      </c>
+      <c r="I34" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35">
+        <v>1388.59</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>61.2</v>
+      </c>
+      <c r="H35" t="s">
+        <v>239</v>
+      </c>
+      <c r="I35" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36">
+        <v>1388.1</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36">
+        <v>44.3</v>
+      </c>
+      <c r="E36" t="s">
+        <v>124</v>
+      </c>
+      <c r="F36" t="s">
+        <v>170</v>
+      </c>
+      <c r="G36" t="s">
+        <v>212</v>
+      </c>
+      <c r="H36" t="s">
+        <v>249</v>
+      </c>
+      <c r="I36" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37">
+        <v>1386.3</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>27.1</v>
+      </c>
+      <c r="E37" t="s">
+        <v>125</v>
+      </c>
+      <c r="F37" t="s">
+        <v>171</v>
+      </c>
+      <c r="G37" t="s">
+        <v>213</v>
+      </c>
+      <c r="H37" t="s">
+        <v>250</v>
+      </c>
+      <c r="I37" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38">
+        <v>1371.9</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38">
+        <v>15.6</v>
+      </c>
+      <c r="H38" t="s">
+        <v>239</v>
+      </c>
+      <c r="I38" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39">
+        <v>1368.5</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39">
+        <v>61.7</v>
+      </c>
+      <c r="H39" t="s">
+        <v>239</v>
+      </c>
+      <c r="I39" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40">
+        <v>1362</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40">
+        <v>59.3</v>
+      </c>
+      <c r="E40" t="s">
+        <v>126</v>
+      </c>
+      <c r="F40" t="s">
+        <v>172</v>
+      </c>
+      <c r="G40" t="s">
+        <v>214</v>
+      </c>
+      <c r="H40" t="s">
+        <v>251</v>
+      </c>
+      <c r="I40" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41">
+        <v>1346.7</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41">
+        <v>56.8</v>
+      </c>
+      <c r="H41" t="s">
+        <v>239</v>
+      </c>
+      <c r="I41" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42">
+        <v>1312.3</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+      <c r="D42">
+        <v>61.9</v>
+      </c>
+      <c r="E42" t="s">
+        <v>127</v>
+      </c>
+      <c r="F42" t="s">
+        <v>173</v>
+      </c>
+      <c r="G42" t="s">
+        <v>215</v>
+      </c>
+      <c r="H42" t="s">
+        <v>252</v>
+      </c>
+      <c r="I42" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43">
+        <v>1306.2</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43">
+        <v>45.7</v>
+      </c>
+      <c r="H43" t="s">
+        <v>239</v>
+      </c>
+      <c r="I43" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44">
+        <v>1299.4</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <v>62.5</v>
+      </c>
+      <c r="H44" t="s">
+        <v>239</v>
+      </c>
+      <c r="I44" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45">
+        <v>1217.62</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45">
+        <v>43.7</v>
+      </c>
+      <c r="E45" t="s">
+        <v>128</v>
+      </c>
+      <c r="F45" t="s">
+        <v>174</v>
+      </c>
+      <c r="G45" t="s">
+        <v>216</v>
+      </c>
+      <c r="H45" t="s">
+        <v>253</v>
+      </c>
+      <c r="I45" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46">
+        <v>1211.3</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46">
+        <v>14.9</v>
+      </c>
+      <c r="H46" t="s">
+        <v>239</v>
+      </c>
+      <c r="I46" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47">
+        <v>1192</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>67.5</v>
+      </c>
+      <c r="E47" t="s">
+        <v>129</v>
+      </c>
+      <c r="F47" t="s">
+        <v>175</v>
+      </c>
+      <c r="G47" t="s">
+        <v>217</v>
+      </c>
+      <c r="H47" t="s">
+        <v>254</v>
+      </c>
+      <c r="I47" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48">
+        <v>1191.07</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+      <c r="D48">
+        <v>53.3</v>
+      </c>
+      <c r="E48" t="s">
+        <v>130</v>
+      </c>
+      <c r="F48" t="s">
+        <v>176</v>
+      </c>
+      <c r="G48" t="s">
+        <v>218</v>
+      </c>
+      <c r="H48" t="s">
+        <v>255</v>
+      </c>
+      <c r="I48" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49">
+        <v>1174.8</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49">
+        <v>68.5</v>
+      </c>
+      <c r="H49" t="s">
+        <v>239</v>
+      </c>
+      <c r="I49" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50">
+        <v>1163.7</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50">
+        <v>55</v>
+      </c>
+      <c r="E50" t="s">
+        <v>131</v>
+      </c>
+      <c r="F50" t="s">
+        <v>177</v>
+      </c>
+      <c r="G50" t="s">
+        <v>219</v>
+      </c>
+      <c r="H50" t="s">
+        <v>256</v>
+      </c>
+      <c r="I50" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51">
+        <v>1150.4</v>
+      </c>
+      <c r="C51">
+        <v>2</v>
+      </c>
+      <c r="D51">
+        <v>36.1</v>
+      </c>
+      <c r="E51" t="s">
+        <v>132</v>
+      </c>
+      <c r="F51" t="s">
+        <v>178</v>
+      </c>
+      <c r="G51" t="s">
+        <v>220</v>
+      </c>
+      <c r="H51" t="s">
+        <v>257</v>
+      </c>
+      <c r="I51" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52">
+        <v>1148.7</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="H52" t="s">
+        <v>239</v>
+      </c>
+      <c r="I52" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53">
+        <v>1144.1</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53">
+        <v>59.6</v>
+      </c>
+      <c r="H53" t="s">
+        <v>239</v>
+      </c>
+      <c r="I53" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54">
+        <v>1141.8</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54">
+        <v>44.6</v>
+      </c>
+      <c r="H54" t="s">
+        <v>239</v>
+      </c>
+      <c r="I54" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55">
+        <v>1127.4</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55">
+        <v>69.5</v>
+      </c>
+      <c r="H55" t="s">
+        <v>239</v>
+      </c>
+      <c r="I55" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56">
+        <v>1121.8</v>
+      </c>
+      <c r="C56">
+        <v>2</v>
+      </c>
+      <c r="D56">
+        <v>64.7</v>
+      </c>
+      <c r="H56" t="s">
+        <v>239</v>
+      </c>
+      <c r="I56" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57">
+        <v>1121.4</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <v>65.5</v>
+      </c>
+      <c r="H57" t="s">
+        <v>239</v>
+      </c>
+      <c r="I57" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58">
+        <v>1114.2</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="D58">
+        <v>49.9</v>
+      </c>
+      <c r="E58" t="s">
+        <v>133</v>
+      </c>
+      <c r="F58" t="s">
+        <v>179</v>
+      </c>
+      <c r="G58" t="s">
+        <v>221</v>
+      </c>
+      <c r="H58" t="s">
+        <v>258</v>
+      </c>
+      <c r="I58" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" t="s">
+        <v>66</v>
+      </c>
+      <c r="B59">
+        <v>1068.4</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59">
+        <v>50.8</v>
+      </c>
+      <c r="H59" t="s">
+        <v>239</v>
+      </c>
+      <c r="I59" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" t="s">
+        <v>67</v>
+      </c>
+      <c r="B60">
+        <v>1049.44</v>
+      </c>
+      <c r="C60">
+        <v>3</v>
+      </c>
+      <c r="D60">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="E60" t="s">
+        <v>134</v>
+      </c>
+      <c r="F60" t="s">
+        <v>180</v>
+      </c>
+      <c r="G60" t="s">
+        <v>222</v>
+      </c>
+      <c r="H60" t="s">
+        <v>259</v>
+      </c>
+      <c r="I60" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" t="s">
+        <v>68</v>
+      </c>
+      <c r="B61">
+        <v>1027.7</v>
+      </c>
+      <c r="C61">
+        <v>2</v>
+      </c>
+      <c r="D61">
+        <v>39.1</v>
+      </c>
+      <c r="H61" t="s">
+        <v>239</v>
+      </c>
+      <c r="I61" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" t="s">
+        <v>69</v>
+      </c>
+      <c r="B62">
+        <v>1024.2</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62">
+        <v>40.1</v>
+      </c>
+      <c r="E62" t="s">
+        <v>135</v>
+      </c>
+      <c r="F62" t="s">
+        <v>181</v>
+      </c>
+      <c r="G62" t="s">
+        <v>223</v>
+      </c>
+      <c r="H62" t="s">
+        <v>260</v>
+      </c>
+      <c r="I62" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" t="s">
+        <v>70</v>
+      </c>
+      <c r="B63">
+        <v>1018.8</v>
+      </c>
+      <c r="C63">
+        <v>2</v>
+      </c>
+      <c r="D63">
+        <v>51.9</v>
+      </c>
+      <c r="E63" t="s">
+        <v>136</v>
+      </c>
+      <c r="F63" t="s">
+        <v>182</v>
+      </c>
+      <c r="G63" t="s">
+        <v>224</v>
+      </c>
+      <c r="H63" t="s">
+        <v>261</v>
+      </c>
+      <c r="I63" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64" t="s">
+        <v>71</v>
+      </c>
+      <c r="B64">
+        <v>1009.62</v>
+      </c>
+      <c r="C64">
+        <v>2</v>
+      </c>
+      <c r="D64">
+        <v>50.7</v>
+      </c>
+      <c r="E64" t="s">
+        <v>137</v>
+      </c>
+      <c r="F64" t="s">
+        <v>183</v>
+      </c>
+      <c r="G64" t="s">
+        <v>225</v>
+      </c>
+      <c r="H64" t="s">
+        <v>262</v>
+      </c>
+      <c r="I64" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65" t="s">
+        <v>72</v>
+      </c>
+      <c r="B65">
+        <v>1004.02</v>
+      </c>
+      <c r="C65">
+        <v>2</v>
+      </c>
+      <c r="D65">
+        <v>45.5</v>
+      </c>
+      <c r="E65" t="s">
+        <v>138</v>
+      </c>
+      <c r="F65" t="s">
+        <v>184</v>
+      </c>
+      <c r="G65" t="s">
+        <v>226</v>
+      </c>
+      <c r="H65" t="s">
+        <v>263</v>
+      </c>
+      <c r="I65" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66" t="s">
+        <v>73</v>
+      </c>
+      <c r="B66">
+        <v>1001.4</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+      <c r="D66">
+        <v>46.9</v>
+      </c>
+      <c r="E66" t="s">
+        <v>139</v>
+      </c>
+      <c r="F66" t="s">
+        <v>185</v>
+      </c>
+      <c r="G66" t="s">
+        <v>227</v>
+      </c>
+      <c r="H66" t="s">
+        <v>264</v>
+      </c>
+      <c r="I66" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" t="s">
+        <v>74</v>
+      </c>
+      <c r="B67">
+        <v>991.1</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
+      <c r="D67">
+        <v>66.7</v>
+      </c>
+      <c r="E67" t="s">
+        <v>140</v>
+      </c>
+      <c r="F67" t="s">
+        <v>186</v>
+      </c>
+      <c r="G67" t="s">
+        <v>228</v>
+      </c>
+      <c r="H67" t="s">
+        <v>265</v>
+      </c>
+      <c r="I67" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68" t="s">
+        <v>75</v>
+      </c>
+      <c r="B68">
+        <v>984.1</v>
+      </c>
+      <c r="C68">
+        <v>2</v>
+      </c>
+      <c r="D68">
+        <v>50</v>
+      </c>
+      <c r="E68" t="s">
+        <v>141</v>
+      </c>
+      <c r="F68" t="s">
+        <v>187</v>
+      </c>
+      <c r="G68" t="s">
+        <v>229</v>
+      </c>
+      <c r="H68" t="s">
+        <v>266</v>
+      </c>
+      <c r="I68" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69" t="s">
+        <v>76</v>
+      </c>
+      <c r="B69">
+        <v>963.6</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+      <c r="D69">
+        <v>56.3</v>
+      </c>
+      <c r="H69" t="s">
+        <v>239</v>
+      </c>
+      <c r="I69" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70" t="s">
+        <v>77</v>
+      </c>
+      <c r="B70">
+        <v>960.7</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+      <c r="D70">
+        <v>27.1</v>
+      </c>
+      <c r="E70" t="s">
+        <v>142</v>
+      </c>
+      <c r="F70" t="s">
+        <v>188</v>
+      </c>
+      <c r="G70" t="s">
+        <v>213</v>
+      </c>
+      <c r="H70" t="s">
+        <v>267</v>
+      </c>
+      <c r="I70" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" t="s">
+        <v>78</v>
+      </c>
+      <c r="B71">
+        <v>955.9</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+      <c r="D71">
+        <v>68.7</v>
+      </c>
+      <c r="E71" t="s">
+        <v>143</v>
+      </c>
+      <c r="F71" t="s">
+        <v>189</v>
+      </c>
+      <c r="G71" t="s">
+        <v>230</v>
+      </c>
+      <c r="H71" t="s">
+        <v>268</v>
+      </c>
+      <c r="I71" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" t="s">
+        <v>79</v>
+      </c>
+      <c r="B72">
+        <v>955</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="E72" t="s">
+        <v>144</v>
+      </c>
+      <c r="F72" t="s">
+        <v>190</v>
+      </c>
+      <c r="G72" t="s">
+        <v>231</v>
+      </c>
+      <c r="H72" t="s">
+        <v>269</v>
+      </c>
+      <c r="I72" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73" t="s">
+        <v>80</v>
+      </c>
+      <c r="B73">
+        <v>949.8</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+      <c r="D73">
+        <v>45.8</v>
+      </c>
+      <c r="H73" t="s">
+        <v>239</v>
+      </c>
+      <c r="I73" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" t="s">
+        <v>81</v>
+      </c>
+      <c r="B74">
+        <v>949.1</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+      <c r="D74">
+        <v>55.9</v>
+      </c>
+      <c r="E74" t="s">
+        <v>145</v>
+      </c>
+      <c r="F74" t="s">
+        <v>191</v>
+      </c>
+      <c r="G74" t="s">
+        <v>232</v>
+      </c>
+      <c r="H74" t="s">
+        <v>270</v>
+      </c>
+      <c r="I74" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" t="s">
+        <v>82</v>
+      </c>
+      <c r="B75">
+        <v>948.8</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+      <c r="D75">
+        <v>52.6</v>
+      </c>
+      <c r="H75" t="s">
+        <v>239</v>
+      </c>
+      <c r="I75" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76" t="s">
+        <v>83</v>
+      </c>
+      <c r="B76">
+        <v>934.7</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+      <c r="D76">
+        <v>9.9</v>
+      </c>
+      <c r="H76" t="s">
+        <v>239</v>
+      </c>
+      <c r="I76" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77" t="s">
+        <v>84</v>
+      </c>
+      <c r="B77">
+        <v>931</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="D77">
+        <v>47.6</v>
+      </c>
+      <c r="H77" t="s">
+        <v>239</v>
+      </c>
+      <c r="I77" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78" t="s">
+        <v>85</v>
+      </c>
+      <c r="B78">
+        <v>924.1</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+      <c r="D78">
+        <v>45.8</v>
+      </c>
+      <c r="H78" t="s">
+        <v>239</v>
+      </c>
+      <c r="I78" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79" t="s">
+        <v>86</v>
+      </c>
+      <c r="B79">
+        <v>921.3</v>
+      </c>
+      <c r="C79">
+        <v>1</v>
+      </c>
+      <c r="D79">
+        <v>61.2</v>
+      </c>
+      <c r="H79" t="s">
+        <v>239</v>
+      </c>
+      <c r="I79" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" t="s">
+        <v>87</v>
+      </c>
+      <c r="B80">
+        <v>920.8</v>
+      </c>
+      <c r="C80">
+        <v>2</v>
+      </c>
+      <c r="D80">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="E80" t="s">
+        <v>146</v>
+      </c>
+      <c r="F80" t="s">
+        <v>192</v>
+      </c>
+      <c r="G80" t="s">
+        <v>233</v>
+      </c>
+      <c r="H80" t="s">
+        <v>271</v>
+      </c>
+      <c r="I80" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" t="s">
+        <v>88</v>
+      </c>
+      <c r="B81">
+        <v>907.6</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+      <c r="D81">
+        <v>27.1</v>
+      </c>
+      <c r="E81" t="s">
+        <v>147</v>
+      </c>
+      <c r="F81" t="s">
+        <v>193</v>
+      </c>
+      <c r="G81" t="s">
+        <v>213</v>
+      </c>
+      <c r="H81" t="s">
+        <v>272</v>
+      </c>
+      <c r="I81" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82" t="s">
+        <v>89</v>
+      </c>
+      <c r="B82">
+        <v>907</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+      <c r="D82">
+        <v>34.1</v>
+      </c>
+      <c r="H82" t="s">
+        <v>239</v>
+      </c>
+      <c r="I82" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83" t="s">
+        <v>90</v>
+      </c>
+      <c r="B83">
+        <v>880.3</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+      <c r="D83">
+        <v>57.3</v>
+      </c>
+      <c r="E83" t="s">
+        <v>148</v>
+      </c>
+      <c r="F83" t="s">
+        <v>194</v>
+      </c>
+      <c r="G83" t="s">
+        <v>234</v>
+      </c>
+      <c r="H83" t="s">
+        <v>273</v>
+      </c>
+      <c r="I83" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" t="s">
+        <v>91</v>
+      </c>
+      <c r="B84">
+        <v>879.6</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
+      <c r="D84">
+        <v>58.4</v>
+      </c>
+      <c r="H84" t="s">
+        <v>239</v>
+      </c>
+      <c r="I84" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
+      <c r="A85" t="s">
+        <v>92</v>
+      </c>
+      <c r="B85">
+        <v>874</v>
+      </c>
+      <c r="C85">
+        <v>2</v>
+      </c>
+      <c r="D85">
+        <v>63</v>
+      </c>
+      <c r="H85" t="s">
+        <v>239</v>
+      </c>
+      <c r="I85" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
+      <c r="A86" t="s">
+        <v>93</v>
+      </c>
+      <c r="B86">
+        <v>871.3</v>
+      </c>
+      <c r="C86">
+        <v>3</v>
+      </c>
+      <c r="D86">
+        <v>29.9</v>
+      </c>
+      <c r="E86" t="s">
+        <v>149</v>
+      </c>
+      <c r="F86" t="s">
+        <v>195</v>
+      </c>
+      <c r="G86" t="s">
+        <v>209</v>
+      </c>
+      <c r="H86" t="s">
+        <v>274</v>
+      </c>
+      <c r="I86" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" t="s">
+        <v>94</v>
+      </c>
+      <c r="B87">
+        <v>870.8</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
+      </c>
+      <c r="D87">
+        <v>26.9</v>
+      </c>
+      <c r="H87" t="s">
+        <v>239</v>
+      </c>
+      <c r="I87" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" t="s">
+        <v>95</v>
+      </c>
+      <c r="B88">
+        <v>865.8</v>
+      </c>
+      <c r="C88">
+        <v>1</v>
+      </c>
+      <c r="D88">
+        <v>57.1</v>
+      </c>
+      <c r="H88" t="s">
+        <v>239</v>
+      </c>
+      <c r="I88" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
+      <c r="A89" t="s">
+        <v>96</v>
+      </c>
+      <c r="B89">
+        <v>864</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
+      <c r="D89">
+        <v>54.6</v>
+      </c>
+      <c r="E89" t="s">
+        <v>150</v>
+      </c>
+      <c r="F89" t="s">
+        <v>196</v>
+      </c>
+      <c r="H89" t="s">
+        <v>239</v>
+      </c>
+      <c r="I89" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
+      <c r="A90" t="s">
+        <v>97</v>
+      </c>
+      <c r="B90">
+        <v>860.7</v>
+      </c>
+      <c r="C90">
+        <v>1</v>
+      </c>
+      <c r="D90">
+        <v>29.9</v>
+      </c>
+      <c r="E90" t="s">
+        <v>151</v>
+      </c>
+      <c r="F90" t="s">
+        <v>197</v>
+      </c>
+      <c r="G90" t="s">
+        <v>209</v>
+      </c>
+      <c r="H90" t="s">
+        <v>275</v>
+      </c>
+      <c r="I90" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
+      <c r="A91" t="s">
+        <v>98</v>
+      </c>
+      <c r="B91">
+        <v>856.89</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
+      <c r="D91">
+        <v>65.5</v>
+      </c>
+      <c r="H91" t="s">
+        <v>239</v>
+      </c>
+      <c r="I91" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
+      <c r="A92" t="s">
+        <v>99</v>
+      </c>
+      <c r="B92">
+        <v>854.1</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+      <c r="D92">
+        <v>29.3</v>
+      </c>
+      <c r="H92" t="s">
+        <v>239</v>
+      </c>
+      <c r="I92" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
+      <c r="A93" t="s">
+        <v>100</v>
+      </c>
+      <c r="B93">
+        <v>852</v>
+      </c>
+      <c r="C93">
+        <v>1</v>
+      </c>
+      <c r="D93">
+        <v>45.7</v>
+      </c>
+      <c r="E93" t="s">
+        <v>152</v>
+      </c>
+      <c r="F93" t="s">
+        <v>198</v>
+      </c>
+      <c r="G93" t="s">
+        <v>235</v>
+      </c>
+      <c r="H93" t="s">
+        <v>276</v>
+      </c>
+      <c r="I93" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
+      <c r="A94" t="s">
+        <v>101</v>
+      </c>
+      <c r="B94">
+        <v>833.3</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
+      <c r="D94">
+        <v>21.6</v>
+      </c>
+      <c r="H94" t="s">
+        <v>239</v>
+      </c>
+      <c r="I94" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
+      <c r="A95" t="s">
+        <v>102</v>
+      </c>
+      <c r="B95">
+        <v>827.6</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
+      <c r="D95">
+        <v>39.7</v>
+      </c>
+      <c r="H95" t="s">
+        <v>239</v>
+      </c>
+      <c r="I95" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="A96" t="s">
+        <v>103</v>
+      </c>
+      <c r="B96">
+        <v>827</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+      <c r="D96">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E96" t="s">
+        <v>153</v>
+      </c>
+      <c r="F96" t="s">
+        <v>199</v>
+      </c>
+      <c r="G96" t="s">
+        <v>236</v>
+      </c>
+      <c r="H96" t="s">
+        <v>277</v>
+      </c>
+      <c r="I96" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
+      <c r="A97" t="s">
+        <v>104</v>
+      </c>
+      <c r="B97">
+        <v>823</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+      <c r="D97">
+        <v>59.5</v>
+      </c>
+      <c r="H97" t="s">
+        <v>239</v>
+      </c>
+      <c r="I97" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" t="s">
+        <v>105</v>
+      </c>
+      <c r="B98">
+        <v>821</v>
+      </c>
+      <c r="C98">
+        <v>2</v>
+      </c>
+      <c r="D98">
+        <v>42.6</v>
+      </c>
+      <c r="E98" t="s">
+        <v>154</v>
+      </c>
+      <c r="F98" t="s">
+        <v>200</v>
+      </c>
+      <c r="G98" t="s">
+        <v>237</v>
+      </c>
+      <c r="H98" t="s">
+        <v>278</v>
+      </c>
+      <c r="I98" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" t="s">
+        <v>106</v>
+      </c>
+      <c r="B99">
+        <v>819</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
+      <c r="D99">
+        <v>54.2</v>
+      </c>
+      <c r="H99" t="s">
+        <v>239</v>
+      </c>
+      <c r="I99" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
+      <c r="A100" t="s">
+        <v>107</v>
+      </c>
+      <c r="B100">
+        <v>817</v>
+      </c>
+      <c r="C100">
+        <v>1</v>
+      </c>
+      <c r="D100">
+        <v>61.2</v>
+      </c>
+      <c r="E100" t="s">
+        <v>155</v>
+      </c>
+      <c r="F100" t="s">
+        <v>201</v>
+      </c>
+      <c r="G100" t="s">
+        <v>238</v>
+      </c>
+      <c r="H100" t="s">
+        <v>279</v>
+      </c>
+      <c r="I100" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
+      <c r="A101" t="s">
+        <v>108</v>
+      </c>
+      <c r="B101">
+        <v>810.7</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
+      <c r="D101">
+        <v>12.2</v>
+      </c>
+      <c r="H101" t="s">
+        <v>239</v>
+      </c>
+      <c r="I101" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
+      <c r="A102" t="s">
+        <v>109</v>
+      </c>
+      <c r="B102">
+        <v>806.2</v>
+      </c>
+      <c r="C102">
+        <v>1</v>
+      </c>
+      <c r="D102">
+        <v>25.7</v>
+      </c>
+      <c r="E102" t="s">
+        <v>156</v>
+      </c>
+      <c r="F102" t="s">
+        <v>202</v>
+      </c>
+      <c r="H102" t="s">
+        <v>239</v>
+      </c>
+      <c r="I102" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
+      <c r="A103" t="s">
         <v>110</v>
       </c>
-      <c r="I34" t="s">
-        <v>110</v>
+      <c r="B103">
+        <v>803.5</v>
+      </c>
+      <c r="C103">
+        <v>1</v>
+      </c>
+      <c r="D103">
+        <v>59.8</v>
+      </c>
+      <c r="H103" t="s">
+        <v>239</v>
+      </c>
+      <c r="I103" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -1727,30 +3776,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>142</v>
+        <v>304</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>143</v>
+        <v>305</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>144</v>
+        <v>306</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>145</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2">
-        <v>60000</v>
+        <v>200000</v>
       </c>
       <c r="B2">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="C2">
-        <v>60413.908</v>
+        <v>200398.465</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/optimalisatie_resultaat.xlsx
+++ b/outputs/optimalisatie_resultaat.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="220">
   <si>
     <t>POSTCODE_KEY</t>
   </si>
@@ -59,6 +59,18 @@
     <t>46569</t>
   </si>
   <si>
+    <t>47447</t>
+  </si>
+  <si>
+    <t>46282</t>
+  </si>
+  <si>
+    <t>41334</t>
+  </si>
+  <si>
+    <t>47906</t>
+  </si>
+  <si>
     <t>47574</t>
   </si>
   <si>
@@ -80,9 +92,15 @@
     <t>3755NM</t>
   </si>
   <si>
+    <t>47803</t>
+  </si>
+  <si>
     <t>6687LD</t>
   </si>
   <si>
+    <t>6026RG</t>
+  </si>
+  <si>
     <t>46519</t>
   </si>
   <si>
@@ -113,15 +131,33 @@
     <t>6741EC</t>
   </si>
   <si>
+    <t>47839</t>
+  </si>
+  <si>
     <t>46414</t>
   </si>
   <si>
     <t>46485</t>
   </si>
   <si>
+    <t>46244</t>
+  </si>
+  <si>
+    <t>4251NE</t>
+  </si>
+  <si>
     <t>7683AZ</t>
   </si>
   <si>
+    <t>46284</t>
+  </si>
+  <si>
+    <t>1394AB</t>
+  </si>
+  <si>
+    <t>47199</t>
+  </si>
+  <si>
     <t>46509</t>
   </si>
   <si>
@@ -140,6 +176,9 @@
     <t>3762LB</t>
   </si>
   <si>
+    <t>1399EP</t>
+  </si>
+  <si>
     <t>47509</t>
   </si>
   <si>
@@ -152,6 +191,9 @@
     <t>6718NG</t>
   </si>
   <si>
+    <t>5595GD</t>
+  </si>
+  <si>
     <t>6874BT</t>
   </si>
   <si>
@@ -170,27 +212,51 @@
     <t>5855AV</t>
   </si>
   <si>
+    <t>5995NT</t>
+  </si>
+  <si>
     <t>47647</t>
   </si>
   <si>
+    <t>6031PX</t>
+  </si>
+  <si>
+    <t>5595XB</t>
+  </si>
+  <si>
     <t>3862PZ</t>
   </si>
   <si>
     <t>6865NA</t>
   </si>
   <si>
+    <t>5524KE</t>
+  </si>
+  <si>
     <t>4214KW</t>
   </si>
   <si>
     <t>5866BR</t>
   </si>
   <si>
+    <t>5591TZ</t>
+  </si>
+  <si>
     <t>47506</t>
   </si>
   <si>
+    <t>5091JS</t>
+  </si>
+  <si>
     <t>4105LE</t>
   </si>
   <si>
+    <t>3481CT</t>
+  </si>
+  <si>
+    <t>7663TE</t>
+  </si>
+  <si>
     <t>3781NN</t>
   </si>
   <si>
@@ -209,147 +275,6 @@
     <t>8251PB</t>
   </si>
   <si>
-    <t>5721PD</t>
-  </si>
-  <si>
-    <t>8102SL</t>
-  </si>
-  <si>
-    <t>8106AG</t>
-  </si>
-  <si>
-    <t>5725RG</t>
-  </si>
-  <si>
-    <t>5845EJ</t>
-  </si>
-  <si>
-    <t>5346JN</t>
-  </si>
-  <si>
-    <t>5425RD</t>
-  </si>
-  <si>
-    <t>5473KG</t>
-  </si>
-  <si>
-    <t>7151HA</t>
-  </si>
-  <si>
-    <t>3941PT</t>
-  </si>
-  <si>
-    <t>8219PE</t>
-  </si>
-  <si>
-    <t>5335LB</t>
-  </si>
-  <si>
-    <t>47661</t>
-  </si>
-  <si>
-    <t>6718SH</t>
-  </si>
-  <si>
-    <t>5613ES</t>
-  </si>
-  <si>
-    <t>5151RH</t>
-  </si>
-  <si>
-    <t>47625</t>
-  </si>
-  <si>
-    <t>5481XN</t>
-  </si>
-  <si>
-    <t>3896LT</t>
-  </si>
-  <si>
-    <t>6909BL</t>
-  </si>
-  <si>
-    <t>8131TC</t>
-  </si>
-  <si>
-    <t>47624</t>
-  </si>
-  <si>
-    <t>3737MN</t>
-  </si>
-  <si>
-    <t>5731PT</t>
-  </si>
-  <si>
-    <t>6718PG</t>
-  </si>
-  <si>
-    <t>7244NA</t>
-  </si>
-  <si>
-    <t>5271VC</t>
-  </si>
-  <si>
-    <t>3723MC</t>
-  </si>
-  <si>
-    <t>1213RM</t>
-  </si>
-  <si>
-    <t>6741HP</t>
-  </si>
-  <si>
-    <t>6615AK</t>
-  </si>
-  <si>
-    <t>5321JE</t>
-  </si>
-  <si>
-    <t>3766AD</t>
-  </si>
-  <si>
-    <t>6741KP</t>
-  </si>
-  <si>
-    <t>5268LE</t>
-  </si>
-  <si>
-    <t>6595MB</t>
-  </si>
-  <si>
-    <t>6624KJ</t>
-  </si>
-  <si>
-    <t>46446</t>
-  </si>
-  <si>
-    <t>7274EM</t>
-  </si>
-  <si>
-    <t>6911KM</t>
-  </si>
-  <si>
-    <t>5324AZ</t>
-  </si>
-  <si>
-    <t>5384RB</t>
-  </si>
-  <si>
-    <t>7461PN</t>
-  </si>
-  <si>
-    <t>3737BL</t>
-  </si>
-  <si>
-    <t>6661NR</t>
-  </si>
-  <si>
-    <t>6603KT</t>
-  </si>
-  <si>
-    <t>3999NR</t>
-  </si>
-  <si>
     <t>Pensionstal De Paardenstek</t>
   </si>
   <si>
@@ -362,6 +287,9 @@
     <t>Vof Stal Paardenvreugd</t>
   </si>
   <si>
+    <t>Lac Hoeve</t>
+  </si>
+  <si>
     <t>Paardenopfokbedrijf Wim Ten Pas</t>
   </si>
   <si>
@@ -380,6 +308,9 @@
     <t>Fred Van Straaten Sport Stables</t>
   </si>
   <si>
+    <t>Pensionstal De Bergen</t>
+  </si>
+  <si>
     <t>Stal Groenendaal BV</t>
   </si>
   <si>
@@ -389,6 +320,9 @@
     <t>Training en Handelstal Johan Laseur B.V.</t>
   </si>
   <si>
+    <t>Any Dale Hippique</t>
+  </si>
+  <si>
     <t>Pensionstal Klein Heiligenberg Vof</t>
   </si>
   <si>
@@ -401,93 +335,39 @@
     <t>Sonniushof Sport Bv</t>
   </si>
   <si>
+    <t>Hx Breeding 2</t>
+  </si>
+  <si>
+    <t>Manege de Molenberg</t>
+  </si>
+  <si>
     <t>Stal Van Laar</t>
   </si>
   <si>
+    <t>Stal Smits</t>
+  </si>
+  <si>
     <t>Opfokstal De Roosahoeve</t>
   </si>
   <si>
     <t>Aniekpoelshorses Bv</t>
   </si>
   <si>
+    <t>RSC Manege Meulendijks</t>
+  </si>
+  <si>
+    <t>Steenhof Stables</t>
+  </si>
+  <si>
     <t>Gh De Leeuw</t>
   </si>
   <si>
+    <t>Stal Denink</t>
+  </si>
+  <si>
     <t>Stal Jacobs</t>
   </si>
   <si>
-    <t>Jjs Winterstalling Opfok</t>
-  </si>
-  <si>
-    <t>Elzenburg Oss Bv</t>
-  </si>
-  <si>
-    <t>Manege Van Erp Vof</t>
-  </si>
-  <si>
-    <t>Springstal Van De Wetering</t>
-  </si>
-  <si>
-    <t>Paardenhouderij Tizzum</t>
-  </si>
-  <si>
-    <t>Lhbm Beusink</t>
-  </si>
-  <si>
-    <t>Firma Maat</t>
-  </si>
-  <si>
-    <t>Aike Wolfs</t>
-  </si>
-  <si>
-    <t>Dutchsportponys</t>
-  </si>
-  <si>
-    <t>Oscarhoeve</t>
-  </si>
-  <si>
-    <t>Jr Stables</t>
-  </si>
-  <si>
-    <t>R Vissers Drunen</t>
-  </si>
-  <si>
-    <t>Stal Witte Bv</t>
-  </si>
-  <si>
-    <t>Demro Stables Bv</t>
-  </si>
-  <si>
-    <t>Hengstenstation Gebr Van Manen Bv</t>
-  </si>
-  <si>
-    <t>Stal Felicia</t>
-  </si>
-  <si>
-    <t>Stal Beiten</t>
-  </si>
-  <si>
-    <t>Nieuw Eldorado</t>
-  </si>
-  <si>
-    <t>Kabeko Doors</t>
-  </si>
-  <si>
-    <t>Hengstenstation Van Uytert Bv</t>
-  </si>
-  <si>
-    <t>Mam Bouwmanwgpm Bouwman Peek</t>
-  </si>
-  <si>
-    <t>Stal De Fliere Fluiter</t>
-  </si>
-  <si>
-    <t>Stal Van Brenk Bv</t>
-  </si>
-  <si>
-    <t>RSC Sint Frans</t>
-  </si>
-  <si>
     <t>Wakkerendijk 31</t>
   </si>
   <si>
@@ -500,6 +380,9 @@
     <t>Geerenweg 10</t>
   </si>
   <si>
+    <t>Hugten 19</t>
+  </si>
+  <si>
     <t>Bataafseweg 8</t>
   </si>
   <si>
@@ -518,6 +401,9 @@
     <t>Ommerweg 74</t>
   </si>
   <si>
+    <t>Meerlaan 23</t>
+  </si>
+  <si>
     <t>Zevenhuizerstraat 154</t>
   </si>
   <si>
@@ -527,6 +413,9 @@
     <t>Jachthuislaan 57</t>
   </si>
   <si>
+    <t>Googweg 9 A</t>
+  </si>
+  <si>
     <t>Ursulineweg 1</t>
   </si>
   <si>
@@ -539,93 +428,39 @@
     <t>Sonniuswijk 35</t>
   </si>
   <si>
+    <t>Rijksweg 43</t>
+  </si>
+  <si>
+    <t>Valkenswaardseweg 29C</t>
+  </si>
+  <si>
     <t>Voorthuizerweg 2</t>
   </si>
   <si>
+    <t>Tasbroekwegje 4</t>
+  </si>
+  <si>
     <t>Molenweg 3</t>
   </si>
   <si>
     <t>Donkstraat 11</t>
   </si>
   <si>
+    <t>Strabrechtseheideweg 6</t>
+  </si>
+  <si>
+    <t>Steenovenweg 1</t>
+  </si>
+  <si>
     <t>Prijsseweg 22</t>
   </si>
   <si>
+    <t>Uelserweg 162</t>
+  </si>
+  <si>
     <t>Hunnenweg 40 A</t>
   </si>
   <si>
-    <t>Hagweg 9</t>
-  </si>
-  <si>
-    <t>Meijelseweg 73</t>
-  </si>
-  <si>
-    <t>Frankenbeemdweg 39</t>
-  </si>
-  <si>
-    <t>Breemhorstsedijk 65</t>
-  </si>
-  <si>
-    <t>Lange Kruisdelstraat 5 c</t>
-  </si>
-  <si>
-    <t>Molenweg 20</t>
-  </si>
-  <si>
-    <t>Molenweg 9</t>
-  </si>
-  <si>
-    <t>Bijlweg 4</t>
-  </si>
-  <si>
-    <t>Veerweg 1 b</t>
-  </si>
-  <si>
-    <t>Deelweg 20</t>
-  </si>
-  <si>
-    <t>Lakerstraat 32</t>
-  </si>
-  <si>
-    <t>Margrietweg 1</t>
-  </si>
-  <si>
-    <t>Olieeindsestraat 8</t>
-  </si>
-  <si>
-    <t>Heezerweg 7</t>
-  </si>
-  <si>
-    <t>Zuiderkade 41</t>
-  </si>
-  <si>
-    <t>Lookertstraat 8</t>
-  </si>
-  <si>
-    <t>Meulunterseweg 66</t>
-  </si>
-  <si>
-    <t>Bosstraat 81</t>
-  </si>
-  <si>
-    <t>Immenweg 12</t>
-  </si>
-  <si>
-    <t>van Heemstraweg 6</t>
-  </si>
-  <si>
-    <t>de Berghoofdseweg 4</t>
-  </si>
-  <si>
-    <t>Wijststraat 16</t>
-  </si>
-  <si>
-    <t>Voordorpsedijk 29</t>
-  </si>
-  <si>
-    <t>Heumenseweg 192</t>
-  </si>
-  <si>
     <t>Emst</t>
   </si>
   <si>
@@ -635,6 +470,9 @@
     <t>Eemnes</t>
   </si>
   <si>
+    <t>Maarheeze</t>
+  </si>
+  <si>
     <t>Winterswijk</t>
   </si>
   <si>
@@ -650,6 +488,9 @@
     <t>Den Ham</t>
   </si>
   <si>
+    <t>Nederhorst den Berg</t>
+  </si>
+  <si>
     <t>Laren</t>
   </si>
   <si>
@@ -665,75 +506,33 @@
     <t>Son en Breugel</t>
   </si>
   <si>
+    <t>Kessel</t>
+  </si>
+  <si>
     <t>Nijkerk</t>
   </si>
   <si>
+    <t>Steensel</t>
+  </si>
+  <si>
     <t>Vuren</t>
   </si>
   <si>
     <t>Swolgen</t>
   </si>
   <si>
+    <t>Oost West en Middelbeers</t>
+  </si>
+  <si>
     <t>Culemborg</t>
   </si>
   <si>
+    <t>Mander</t>
+  </si>
+  <si>
     <t>Voorthuizen</t>
   </si>
   <si>
-    <t>Raalte</t>
-  </si>
-  <si>
-    <t>Heusden</t>
-  </si>
-  <si>
-    <t>Oss</t>
-  </si>
-  <si>
-    <t>De Mortel</t>
-  </si>
-  <si>
-    <t>Heeswijk-Dinther</t>
-  </si>
-  <si>
-    <t>Eibergen</t>
-  </si>
-  <si>
-    <t>Doorn</t>
-  </si>
-  <si>
-    <t>Lelystad</t>
-  </si>
-  <si>
-    <t>Alem</t>
-  </si>
-  <si>
-    <t>Eindhoven</t>
-  </si>
-  <si>
-    <t>Drunen</t>
-  </si>
-  <si>
-    <t>Schijndel</t>
-  </si>
-  <si>
-    <t>Mierlo</t>
-  </si>
-  <si>
-    <t>Sint-Michielsgestel</t>
-  </si>
-  <si>
-    <t>Heerewaarden</t>
-  </si>
-  <si>
-    <t>Pannerden</t>
-  </si>
-  <si>
-    <t>Heesch</t>
-  </si>
-  <si>
-    <t>Groenekan</t>
-  </si>
-  <si>
     <t>nan</t>
   </si>
   <si>
@@ -746,6 +545,9 @@
     <t>32164734</t>
   </si>
   <si>
+    <t>77045599</t>
+  </si>
+  <si>
     <t>69709017</t>
   </si>
   <si>
@@ -761,6 +563,9 @@
     <t>63446030</t>
   </si>
   <si>
+    <t>32081621</t>
+  </si>
+  <si>
     <t>76671992</t>
   </si>
   <si>
@@ -776,87 +581,33 @@
     <t>50208012</t>
   </si>
   <si>
+    <t>12058109</t>
+  </si>
+  <si>
     <t>32079020</t>
   </si>
   <si>
+    <t>17270318</t>
+  </si>
+  <si>
     <t>75831112</t>
   </si>
   <si>
     <t>63904810</t>
   </si>
   <si>
+    <t>17207791</t>
+  </si>
+  <si>
     <t>30269767</t>
   </si>
   <si>
+    <t>52336735</t>
+  </si>
+  <si>
     <t>8195043</t>
   </si>
   <si>
-    <t>5073786</t>
-  </si>
-  <si>
-    <t>17131559</t>
-  </si>
-  <si>
-    <t>16056989</t>
-  </si>
-  <si>
-    <t>17168352</t>
-  </si>
-  <si>
-    <t>69929602</t>
-  </si>
-  <si>
-    <t>9213870</t>
-  </si>
-  <si>
-    <t>33207363</t>
-  </si>
-  <si>
-    <t>39071088</t>
-  </si>
-  <si>
-    <t>66265193</t>
-  </si>
-  <si>
-    <t>9137189</t>
-  </si>
-  <si>
-    <t>55069665</t>
-  </si>
-  <si>
-    <t>17270867</t>
-  </si>
-  <si>
-    <t>16043191</t>
-  </si>
-  <si>
-    <t>12056954</t>
-  </si>
-  <si>
-    <t>72005335</t>
-  </si>
-  <si>
-    <t>16039972</t>
-  </si>
-  <si>
-    <t>78101441</t>
-  </si>
-  <si>
-    <t>8225399</t>
-  </si>
-  <si>
-    <t>56863632</t>
-  </si>
-  <si>
-    <t>9211980</t>
-  </si>
-  <si>
-    <t>17245420</t>
-  </si>
-  <si>
-    <t>74470132</t>
-  </si>
-  <si>
     <t>035-5314656</t>
   </si>
   <si>
@@ -872,12 +623,18 @@
     <t>033-2861456</t>
   </si>
   <si>
+    <t>0294 257 514</t>
+  </si>
+  <si>
     <t>033-4564429</t>
   </si>
   <si>
     <t>088- 02 24 300</t>
   </si>
   <si>
+    <t>651807539</t>
+  </si>
+  <si>
     <t>06 51921782</t>
   </si>
   <si>
@@ -887,46 +644,25 @@
     <t>0499 472 133</t>
   </si>
   <si>
+    <t>621871317</t>
+  </si>
+  <si>
     <t>06 29044423</t>
   </si>
   <si>
+    <t>0497 512 684</t>
+  </si>
+  <si>
+    <t>612708022</t>
+  </si>
+  <si>
+    <t>06 25150557</t>
+  </si>
+  <si>
     <t>0345 535 700</t>
   </si>
   <si>
     <t>06 16134328</t>
-  </si>
-  <si>
-    <t>0412 636 602</t>
-  </si>
-  <si>
-    <t>06 53842131</t>
-  </si>
-  <si>
-    <t>06 20515697</t>
-  </si>
-  <si>
-    <t>0343 522 002</t>
-  </si>
-  <si>
-    <t>06 29414477</t>
-  </si>
-  <si>
-    <t>073 547 5928</t>
-  </si>
-  <si>
-    <t>06 55130055</t>
-  </si>
-  <si>
-    <t>035-6018803</t>
-  </si>
-  <si>
-    <t>0412 451 350</t>
-  </si>
-  <si>
-    <t>030 272 3755</t>
-  </si>
-  <si>
-    <t>024-6412218</t>
   </si>
   <si>
     <t>Target_tons_per_year</t>
@@ -1296,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I103"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1342,16 +1078,16 @@
         <v>60.4</v>
       </c>
       <c r="E2" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="F2" t="s">
-        <v>157</v>
+        <v>117</v>
       </c>
       <c r="H2" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I2" t="s">
-        <v>280</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1368,10 +1104,10 @@
         <v>56.9</v>
       </c>
       <c r="H3" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I3" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1388,10 +1124,10 @@
         <v>20.6</v>
       </c>
       <c r="H4" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I4" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1408,10 +1144,10 @@
         <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I5" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1428,10 +1164,10 @@
         <v>63.7</v>
       </c>
       <c r="H6" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I6" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1439,19 +1175,19 @@
         <v>14</v>
       </c>
       <c r="B7">
-        <v>3602</v>
+        <v>4389.7</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>33.7</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="H7" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I7" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1459,19 +1195,19 @@
         <v>15</v>
       </c>
       <c r="B8">
-        <v>3546.99</v>
+        <v>4079.74</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>56.3</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="H8" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I8" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1479,19 +1215,19 @@
         <v>16</v>
       </c>
       <c r="B9">
-        <v>3363.22</v>
+        <v>3992.16</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9">
-        <v>50.6</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H9" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I9" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1499,19 +1235,19 @@
         <v>17</v>
       </c>
       <c r="B10">
-        <v>3239.5</v>
+        <v>3662.9</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>68.2</v>
+        <v>72.7</v>
       </c>
       <c r="H10" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I10" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1519,28 +1255,19 @@
         <v>18</v>
       </c>
       <c r="B11">
-        <v>3208.28</v>
+        <v>3602</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>39</v>
-      </c>
-      <c r="E11" t="s">
-        <v>112</v>
-      </c>
-      <c r="F11" t="s">
-        <v>158</v>
-      </c>
-      <c r="G11" t="s">
-        <v>203</v>
+        <v>33.7</v>
       </c>
       <c r="H11" t="s">
-        <v>240</v>
+        <v>172</v>
       </c>
       <c r="I11" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1548,28 +1275,19 @@
         <v>19</v>
       </c>
       <c r="B12">
-        <v>2755.21</v>
+        <v>3546.99</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>65.40000000000001</v>
-      </c>
-      <c r="E12" t="s">
-        <v>113</v>
-      </c>
-      <c r="F12" t="s">
-        <v>159</v>
-      </c>
-      <c r="G12" t="s">
-        <v>204</v>
+        <v>56.3</v>
       </c>
       <c r="H12" t="s">
-        <v>241</v>
+        <v>172</v>
       </c>
       <c r="I12" t="s">
-        <v>281</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1577,28 +1295,19 @@
         <v>20</v>
       </c>
       <c r="B13">
-        <v>2540.1</v>
+        <v>3363.22</v>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>60.4</v>
-      </c>
-      <c r="E13" t="s">
-        <v>114</v>
-      </c>
-      <c r="F13" t="s">
-        <v>160</v>
-      </c>
-      <c r="G13" t="s">
-        <v>205</v>
+        <v>50.6</v>
       </c>
       <c r="H13" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="I13" t="s">
-        <v>282</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1606,19 +1315,19 @@
         <v>21</v>
       </c>
       <c r="B14">
-        <v>2506.3</v>
+        <v>3239.5</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14">
-        <v>7.1</v>
+        <v>68.2</v>
       </c>
       <c r="H14" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I14" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1626,19 +1335,28 @@
         <v>22</v>
       </c>
       <c r="B15">
-        <v>2221</v>
+        <v>3208.28</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15">
-        <v>55.1</v>
+        <v>39</v>
+      </c>
+      <c r="E15" t="s">
+        <v>87</v>
+      </c>
+      <c r="F15" t="s">
+        <v>118</v>
+      </c>
+      <c r="G15" t="s">
+        <v>148</v>
       </c>
       <c r="H15" t="s">
-        <v>239</v>
+        <v>173</v>
       </c>
       <c r="I15" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1646,19 +1364,28 @@
         <v>23</v>
       </c>
       <c r="B16">
-        <v>2175.8</v>
+        <v>2755.21</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>31.5</v>
+        <v>65.40000000000001</v>
+      </c>
+      <c r="E16" t="s">
+        <v>88</v>
+      </c>
+      <c r="F16" t="s">
+        <v>119</v>
+      </c>
+      <c r="G16" t="s">
+        <v>149</v>
       </c>
       <c r="H16" t="s">
-        <v>239</v>
+        <v>174</v>
       </c>
       <c r="I16" t="s">
-        <v>239</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1666,19 +1393,28 @@
         <v>24</v>
       </c>
       <c r="B17">
-        <v>2127.6</v>
+        <v>2540.1</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17">
-        <v>38.1</v>
+        <v>60.4</v>
+      </c>
+      <c r="E17" t="s">
+        <v>89</v>
+      </c>
+      <c r="F17" t="s">
+        <v>120</v>
+      </c>
+      <c r="G17" t="s">
+        <v>150</v>
       </c>
       <c r="H17" t="s">
-        <v>239</v>
+        <v>175</v>
       </c>
       <c r="I17" t="s">
-        <v>239</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1686,28 +1422,19 @@
         <v>25</v>
       </c>
       <c r="B18">
-        <v>1992.94</v>
+        <v>2509</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18">
-        <v>48.7</v>
-      </c>
-      <c r="E18" t="s">
-        <v>115</v>
-      </c>
-      <c r="F18" t="s">
-        <v>161</v>
-      </c>
-      <c r="G18" t="s">
-        <v>206</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="H18" t="s">
-        <v>243</v>
+        <v>172</v>
       </c>
       <c r="I18" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1715,19 +1442,19 @@
         <v>26</v>
       </c>
       <c r="B19">
-        <v>1948</v>
+        <v>2506.3</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>68.09999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="H19" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I19" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1735,28 +1462,28 @@
         <v>27</v>
       </c>
       <c r="B20">
-        <v>1883.2</v>
+        <v>2292.94</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20">
-        <v>39.7</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="E20" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="F20" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="G20" t="s">
-        <v>207</v>
+        <v>151</v>
       </c>
       <c r="H20" t="s">
-        <v>244</v>
+        <v>176</v>
       </c>
       <c r="I20" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1764,28 +1491,19 @@
         <v>28</v>
       </c>
       <c r="B21">
-        <v>1869.7</v>
+        <v>2221</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21">
-        <v>63.3</v>
-      </c>
-      <c r="E21" t="s">
-        <v>117</v>
-      </c>
-      <c r="F21" t="s">
-        <v>163</v>
-      </c>
-      <c r="G21" t="s">
-        <v>208</v>
+        <v>55.1</v>
       </c>
       <c r="H21" t="s">
-        <v>245</v>
+        <v>172</v>
       </c>
       <c r="I21" t="s">
-        <v>283</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1793,25 +1511,19 @@
         <v>29</v>
       </c>
       <c r="B22">
-        <v>1840.9</v>
+        <v>2175.8</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22">
-        <v>42.3</v>
-      </c>
-      <c r="E22" t="s">
-        <v>118</v>
-      </c>
-      <c r="F22" t="s">
-        <v>164</v>
+        <v>31.5</v>
       </c>
       <c r="H22" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I22" t="s">
-        <v>284</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1819,19 +1531,19 @@
         <v>30</v>
       </c>
       <c r="B23">
-        <v>1822</v>
+        <v>2127.6</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23">
-        <v>60.4</v>
+        <v>38.1</v>
       </c>
       <c r="H23" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I23" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1839,28 +1551,28 @@
         <v>31</v>
       </c>
       <c r="B24">
-        <v>1805.94</v>
+        <v>1992.94</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24">
-        <v>29.9</v>
+        <v>48.7</v>
       </c>
       <c r="E24" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="F24" t="s">
-        <v>165</v>
+        <v>122</v>
       </c>
       <c r="G24" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="H24" t="s">
-        <v>246</v>
+        <v>177</v>
       </c>
       <c r="I24" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1868,19 +1580,19 @@
         <v>32</v>
       </c>
       <c r="B25">
-        <v>1759.1</v>
+        <v>1948</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25">
-        <v>49.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="H25" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I25" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1888,19 +1600,28 @@
         <v>33</v>
       </c>
       <c r="B26">
-        <v>1696.9</v>
+        <v>1883.2</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26">
-        <v>57.1</v>
+        <v>39.7</v>
+      </c>
+      <c r="E26" t="s">
+        <v>92</v>
+      </c>
+      <c r="F26" t="s">
+        <v>123</v>
+      </c>
+      <c r="G26" t="s">
+        <v>153</v>
       </c>
       <c r="H26" t="s">
-        <v>239</v>
+        <v>178</v>
       </c>
       <c r="I26" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1908,28 +1629,28 @@
         <v>34</v>
       </c>
       <c r="B27">
-        <v>1624.9</v>
+        <v>1869.7</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>64.40000000000001</v>
+        <v>63.3</v>
       </c>
       <c r="E27" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="F27" t="s">
-        <v>166</v>
+        <v>124</v>
       </c>
       <c r="G27" t="s">
-        <v>210</v>
+        <v>154</v>
       </c>
       <c r="H27" t="s">
-        <v>247</v>
+        <v>179</v>
       </c>
       <c r="I27" t="s">
-        <v>239</v>
+        <v>200</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1937,19 +1658,25 @@
         <v>35</v>
       </c>
       <c r="B28">
-        <v>1535.6</v>
+        <v>1840.9</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28">
-        <v>45.8</v>
+        <v>42.3</v>
+      </c>
+      <c r="E28" t="s">
+        <v>94</v>
+      </c>
+      <c r="F28" t="s">
+        <v>125</v>
       </c>
       <c r="H28" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I28" t="s">
-        <v>239</v>
+        <v>201</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1957,19 +1684,19 @@
         <v>36</v>
       </c>
       <c r="B29">
-        <v>1517.4</v>
+        <v>1822</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
       <c r="D29">
-        <v>47.4</v>
+        <v>60.4</v>
       </c>
       <c r="H29" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I29" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1977,25 +1704,28 @@
         <v>37</v>
       </c>
       <c r="B30">
-        <v>1505.9</v>
+        <v>1805.94</v>
       </c>
       <c r="C30">
         <v>1</v>
       </c>
       <c r="D30">
-        <v>52.9</v>
+        <v>29.9</v>
       </c>
       <c r="E30" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="F30" t="s">
-        <v>167</v>
+        <v>126</v>
+      </c>
+      <c r="G30" t="s">
+        <v>155</v>
       </c>
       <c r="H30" t="s">
-        <v>239</v>
+        <v>180</v>
       </c>
       <c r="I30" t="s">
-        <v>285</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -2003,19 +1733,19 @@
         <v>38</v>
       </c>
       <c r="B31">
-        <v>1473.8</v>
+        <v>1794.8</v>
       </c>
       <c r="C31">
         <v>1</v>
       </c>
       <c r="D31">
-        <v>59.4</v>
+        <v>74.2</v>
       </c>
       <c r="H31" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I31" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -2023,28 +1753,19 @@
         <v>39</v>
       </c>
       <c r="B32">
-        <v>1452.3</v>
+        <v>1759.1</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32">
-        <v>35.5</v>
-      </c>
-      <c r="E32" t="s">
-        <v>122</v>
-      </c>
-      <c r="F32" t="s">
-        <v>168</v>
-      </c>
-      <c r="G32" t="s">
-        <v>211</v>
+        <v>49.2</v>
       </c>
       <c r="H32" t="s">
-        <v>248</v>
+        <v>172</v>
       </c>
       <c r="I32" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -2052,25 +1773,19 @@
         <v>40</v>
       </c>
       <c r="B33">
-        <v>1442.7</v>
+        <v>1696.9</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>55.2</v>
-      </c>
-      <c r="E33" t="s">
-        <v>123</v>
-      </c>
-      <c r="F33" t="s">
-        <v>169</v>
+        <v>57.1</v>
       </c>
       <c r="H33" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I33" t="s">
-        <v>286</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -2078,19 +1793,19 @@
         <v>41</v>
       </c>
       <c r="B34">
-        <v>1400.9</v>
+        <v>1648.6</v>
       </c>
       <c r="C34">
         <v>1</v>
       </c>
       <c r="D34">
-        <v>63.9</v>
+        <v>74</v>
       </c>
       <c r="H34" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I34" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -2098,19 +1813,19 @@
         <v>42</v>
       </c>
       <c r="B35">
-        <v>1388.59</v>
+        <v>1633</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
       <c r="D35">
-        <v>61.2</v>
+        <v>78.8</v>
       </c>
       <c r="H35" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I35" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -2118,28 +1833,28 @@
         <v>43</v>
       </c>
       <c r="B36">
-        <v>1388.1</v>
+        <v>1624.9</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36">
-        <v>44.3</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="E36" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="F36" t="s">
-        <v>170</v>
+        <v>127</v>
       </c>
       <c r="G36" t="s">
-        <v>212</v>
+        <v>156</v>
       </c>
       <c r="H36" t="s">
-        <v>249</v>
+        <v>181</v>
       </c>
       <c r="I36" t="s">
-        <v>287</v>
+        <v>172</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -2147,28 +1862,19 @@
         <v>44</v>
       </c>
       <c r="B37">
-        <v>1386.3</v>
+        <v>1615.98</v>
       </c>
       <c r="C37">
         <v>1</v>
       </c>
       <c r="D37">
-        <v>27.1</v>
-      </c>
-      <c r="E37" t="s">
-        <v>125</v>
-      </c>
-      <c r="F37" t="s">
-        <v>171</v>
-      </c>
-      <c r="G37" t="s">
-        <v>213</v>
+        <v>72.7</v>
       </c>
       <c r="H37" t="s">
-        <v>250</v>
+        <v>172</v>
       </c>
       <c r="I37" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -2176,19 +1882,28 @@
         <v>45</v>
       </c>
       <c r="B38">
-        <v>1371.9</v>
+        <v>1588.5</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38">
-        <v>15.6</v>
+        <v>73.09999999999999</v>
+      </c>
+      <c r="E38" t="s">
+        <v>97</v>
+      </c>
+      <c r="F38" t="s">
+        <v>128</v>
+      </c>
+      <c r="G38" t="s">
+        <v>157</v>
       </c>
       <c r="H38" t="s">
-        <v>239</v>
+        <v>182</v>
       </c>
       <c r="I38" t="s">
-        <v>239</v>
+        <v>202</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -2196,19 +1911,19 @@
         <v>46</v>
       </c>
       <c r="B39">
-        <v>1368.5</v>
+        <v>1536.7</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
       <c r="D39">
-        <v>61.7</v>
+        <v>78.2</v>
       </c>
       <c r="H39" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I39" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -2216,28 +1931,19 @@
         <v>47</v>
       </c>
       <c r="B40">
-        <v>1362</v>
+        <v>1535.6</v>
       </c>
       <c r="C40">
         <v>1</v>
       </c>
       <c r="D40">
-        <v>59.3</v>
-      </c>
-      <c r="E40" t="s">
-        <v>126</v>
-      </c>
-      <c r="F40" t="s">
-        <v>172</v>
-      </c>
-      <c r="G40" t="s">
-        <v>214</v>
+        <v>45.8</v>
       </c>
       <c r="H40" t="s">
-        <v>251</v>
+        <v>172</v>
       </c>
       <c r="I40" t="s">
-        <v>288</v>
+        <v>172</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -2245,19 +1951,19 @@
         <v>48</v>
       </c>
       <c r="B41">
-        <v>1346.7</v>
+        <v>1517.4</v>
       </c>
       <c r="C41">
         <v>1</v>
       </c>
       <c r="D41">
-        <v>56.8</v>
+        <v>47.4</v>
       </c>
       <c r="H41" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I41" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -2265,28 +1971,25 @@
         <v>49</v>
       </c>
       <c r="B42">
-        <v>1312.3</v>
+        <v>1505.9</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42">
-        <v>61.9</v>
+        <v>52.9</v>
       </c>
       <c r="E42" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="F42" t="s">
-        <v>173</v>
-      </c>
-      <c r="G42" t="s">
-        <v>215</v>
+        <v>129</v>
       </c>
       <c r="H42" t="s">
-        <v>252</v>
+        <v>172</v>
       </c>
       <c r="I42" t="s">
-        <v>289</v>
+        <v>203</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -2294,19 +1997,19 @@
         <v>50</v>
       </c>
       <c r="B43">
-        <v>1306.2</v>
+        <v>1473.8</v>
       </c>
       <c r="C43">
         <v>1</v>
       </c>
       <c r="D43">
-        <v>45.7</v>
+        <v>59.4</v>
       </c>
       <c r="H43" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I43" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -2314,19 +2017,28 @@
         <v>51</v>
       </c>
       <c r="B44">
-        <v>1299.4</v>
+        <v>1452.3</v>
       </c>
       <c r="C44">
         <v>1</v>
       </c>
       <c r="D44">
-        <v>62.5</v>
+        <v>35.5</v>
+      </c>
+      <c r="E44" t="s">
+        <v>99</v>
+      </c>
+      <c r="F44" t="s">
+        <v>130</v>
+      </c>
+      <c r="G44" t="s">
+        <v>158</v>
       </c>
       <c r="H44" t="s">
-        <v>239</v>
+        <v>183</v>
       </c>
       <c r="I44" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -2334,28 +2046,25 @@
         <v>52</v>
       </c>
       <c r="B45">
-        <v>1217.62</v>
+        <v>1442.7</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45">
-        <v>43.7</v>
+        <v>55.2</v>
       </c>
       <c r="E45" t="s">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="F45" t="s">
-        <v>174</v>
-      </c>
-      <c r="G45" t="s">
-        <v>216</v>
+        <v>131</v>
       </c>
       <c r="H45" t="s">
-        <v>253</v>
+        <v>172</v>
       </c>
       <c r="I45" t="s">
-        <v>290</v>
+        <v>204</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -2363,19 +2072,25 @@
         <v>53</v>
       </c>
       <c r="B46">
-        <v>1211.3</v>
+        <v>1419.5</v>
       </c>
       <c r="C46">
         <v>1</v>
       </c>
       <c r="D46">
-        <v>14.9</v>
+        <v>72.7</v>
+      </c>
+      <c r="E46" t="s">
+        <v>101</v>
+      </c>
+      <c r="F46" t="s">
+        <v>132</v>
       </c>
       <c r="H46" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I46" t="s">
-        <v>239</v>
+        <v>205</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -2383,28 +2098,19 @@
         <v>54</v>
       </c>
       <c r="B47">
-        <v>1192</v>
+        <v>1400.9</v>
       </c>
       <c r="C47">
         <v>1</v>
       </c>
       <c r="D47">
-        <v>67.5</v>
-      </c>
-      <c r="E47" t="s">
-        <v>129</v>
-      </c>
-      <c r="F47" t="s">
-        <v>175</v>
-      </c>
-      <c r="G47" t="s">
-        <v>217</v>
+        <v>63.9</v>
       </c>
       <c r="H47" t="s">
-        <v>254</v>
+        <v>172</v>
       </c>
       <c r="I47" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -2412,28 +2118,19 @@
         <v>55</v>
       </c>
       <c r="B48">
-        <v>1191.07</v>
+        <v>1388.59</v>
       </c>
       <c r="C48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48">
-        <v>53.3</v>
-      </c>
-      <c r="E48" t="s">
-        <v>130</v>
-      </c>
-      <c r="F48" t="s">
-        <v>176</v>
-      </c>
-      <c r="G48" t="s">
-        <v>218</v>
+        <v>61.2</v>
       </c>
       <c r="H48" t="s">
-        <v>255</v>
+        <v>172</v>
       </c>
       <c r="I48" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -2441,19 +2138,28 @@
         <v>56</v>
       </c>
       <c r="B49">
-        <v>1174.8</v>
+        <v>1388.1</v>
       </c>
       <c r="C49">
         <v>1</v>
       </c>
       <c r="D49">
-        <v>68.5</v>
+        <v>44.3</v>
+      </c>
+      <c r="E49" t="s">
+        <v>102</v>
+      </c>
+      <c r="F49" t="s">
+        <v>133</v>
+      </c>
+      <c r="G49" t="s">
+        <v>159</v>
       </c>
       <c r="H49" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="I49" t="s">
-        <v>239</v>
+        <v>206</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -2461,28 +2167,28 @@
         <v>57</v>
       </c>
       <c r="B50">
-        <v>1163.7</v>
+        <v>1386.3</v>
       </c>
       <c r="C50">
         <v>1</v>
       </c>
       <c r="D50">
-        <v>55</v>
+        <v>27.1</v>
       </c>
       <c r="E50" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="F50" t="s">
-        <v>177</v>
+        <v>134</v>
       </c>
       <c r="G50" t="s">
-        <v>219</v>
+        <v>160</v>
       </c>
       <c r="H50" t="s">
-        <v>256</v>
+        <v>185</v>
       </c>
       <c r="I50" t="s">
-        <v>291</v>
+        <v>172</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -2490,28 +2196,19 @@
         <v>58</v>
       </c>
       <c r="B51">
-        <v>1150.4</v>
+        <v>1377.84</v>
       </c>
       <c r="C51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51">
-        <v>36.1</v>
-      </c>
-      <c r="E51" t="s">
-        <v>132</v>
-      </c>
-      <c r="F51" t="s">
-        <v>178</v>
-      </c>
-      <c r="G51" t="s">
-        <v>220</v>
+        <v>75.8</v>
       </c>
       <c r="H51" t="s">
-        <v>257</v>
+        <v>172</v>
       </c>
       <c r="I51" t="s">
-        <v>292</v>
+        <v>172</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -2519,19 +2216,19 @@
         <v>59</v>
       </c>
       <c r="B52">
-        <v>1148.7</v>
+        <v>1371.9</v>
       </c>
       <c r="C52">
         <v>1</v>
       </c>
       <c r="D52">
-        <v>68.40000000000001</v>
+        <v>15.6</v>
       </c>
       <c r="H52" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I52" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -2539,19 +2236,19 @@
         <v>60</v>
       </c>
       <c r="B53">
-        <v>1144.1</v>
+        <v>1368.5</v>
       </c>
       <c r="C53">
         <v>1</v>
       </c>
       <c r="D53">
-        <v>59.6</v>
+        <v>61.7</v>
       </c>
       <c r="H53" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I53" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -2559,19 +2256,28 @@
         <v>61</v>
       </c>
       <c r="B54">
-        <v>1141.8</v>
+        <v>1362</v>
       </c>
       <c r="C54">
         <v>1</v>
       </c>
       <c r="D54">
-        <v>44.6</v>
+        <v>59.3</v>
+      </c>
+      <c r="E54" t="s">
+        <v>104</v>
+      </c>
+      <c r="F54" t="s">
+        <v>135</v>
+      </c>
+      <c r="G54" t="s">
+        <v>161</v>
       </c>
       <c r="H54" t="s">
-        <v>239</v>
+        <v>186</v>
       </c>
       <c r="I54" t="s">
-        <v>239</v>
+        <v>207</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -2579,19 +2285,19 @@
         <v>62</v>
       </c>
       <c r="B55">
-        <v>1127.4</v>
+        <v>1346.7</v>
       </c>
       <c r="C55">
         <v>1</v>
       </c>
       <c r="D55">
-        <v>69.5</v>
+        <v>56.8</v>
       </c>
       <c r="H55" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I55" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -2599,19 +2305,28 @@
         <v>63</v>
       </c>
       <c r="B56">
-        <v>1121.8</v>
+        <v>1312.3</v>
       </c>
       <c r="C56">
         <v>2</v>
       </c>
       <c r="D56">
-        <v>64.7</v>
+        <v>61.9</v>
+      </c>
+      <c r="E56" t="s">
+        <v>105</v>
+      </c>
+      <c r="F56" t="s">
+        <v>136</v>
+      </c>
+      <c r="G56" t="s">
+        <v>162</v>
       </c>
       <c r="H56" t="s">
-        <v>239</v>
+        <v>187</v>
       </c>
       <c r="I56" t="s">
-        <v>239</v>
+        <v>208</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -2619,19 +2334,19 @@
         <v>64</v>
       </c>
       <c r="B57">
-        <v>1121.4</v>
+        <v>1306.2</v>
       </c>
       <c r="C57">
         <v>1</v>
       </c>
       <c r="D57">
-        <v>65.5</v>
+        <v>45.7</v>
       </c>
       <c r="H57" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I57" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -2639,28 +2354,28 @@
         <v>65</v>
       </c>
       <c r="B58">
-        <v>1114.2</v>
+        <v>1303.7</v>
       </c>
       <c r="C58">
         <v>1</v>
       </c>
       <c r="D58">
-        <v>49.9</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="E58" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="F58" t="s">
-        <v>179</v>
+        <v>137</v>
       </c>
       <c r="G58" t="s">
-        <v>221</v>
+        <v>163</v>
       </c>
       <c r="H58" t="s">
-        <v>258</v>
+        <v>188</v>
       </c>
       <c r="I58" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -2668,19 +2383,19 @@
         <v>66</v>
       </c>
       <c r="B59">
-        <v>1068.4</v>
+        <v>1299.4</v>
       </c>
       <c r="C59">
         <v>1</v>
       </c>
       <c r="D59">
-        <v>50.8</v>
+        <v>62.5</v>
       </c>
       <c r="H59" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I59" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -2688,28 +2403,19 @@
         <v>67</v>
       </c>
       <c r="B60">
-        <v>1049.44</v>
+        <v>1267.4</v>
       </c>
       <c r="C60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D60">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="E60" t="s">
-        <v>134</v>
-      </c>
-      <c r="F60" t="s">
-        <v>180</v>
-      </c>
-      <c r="G60" t="s">
-        <v>222</v>
+        <v>78</v>
       </c>
       <c r="H60" t="s">
-        <v>259</v>
+        <v>172</v>
       </c>
       <c r="I60" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -2717,19 +2423,25 @@
         <v>68</v>
       </c>
       <c r="B61">
-        <v>1027.7</v>
+        <v>1253.4</v>
       </c>
       <c r="C61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D61">
-        <v>39.1</v>
+        <v>75.8</v>
+      </c>
+      <c r="E61" t="s">
+        <v>107</v>
+      </c>
+      <c r="F61" t="s">
+        <v>138</v>
       </c>
       <c r="H61" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I61" t="s">
-        <v>239</v>
+        <v>209</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -2737,28 +2449,28 @@
         <v>69</v>
       </c>
       <c r="B62">
-        <v>1024.2</v>
+        <v>1217.62</v>
       </c>
       <c r="C62">
         <v>1</v>
       </c>
       <c r="D62">
-        <v>40.1</v>
+        <v>43.7</v>
       </c>
       <c r="E62" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="F62" t="s">
-        <v>181</v>
+        <v>139</v>
       </c>
       <c r="G62" t="s">
-        <v>223</v>
+        <v>164</v>
       </c>
       <c r="H62" t="s">
-        <v>260</v>
+        <v>189</v>
       </c>
       <c r="I62" t="s">
-        <v>293</v>
+        <v>210</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -2766,28 +2478,19 @@
         <v>70</v>
       </c>
       <c r="B63">
-        <v>1018.8</v>
+        <v>1211.3</v>
       </c>
       <c r="C63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D63">
-        <v>51.9</v>
-      </c>
-      <c r="E63" t="s">
-        <v>136</v>
-      </c>
-      <c r="F63" t="s">
-        <v>182</v>
-      </c>
-      <c r="G63" t="s">
-        <v>224</v>
+        <v>14.9</v>
       </c>
       <c r="H63" t="s">
-        <v>261</v>
+        <v>172</v>
       </c>
       <c r="I63" t="s">
-        <v>294</v>
+        <v>172</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -2795,28 +2498,28 @@
         <v>71</v>
       </c>
       <c r="B64">
-        <v>1009.62</v>
+        <v>1194.2</v>
       </c>
       <c r="C64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D64">
-        <v>50.7</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="E64" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="F64" t="s">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="G64" t="s">
-        <v>225</v>
+        <v>165</v>
       </c>
       <c r="H64" t="s">
-        <v>262</v>
+        <v>190</v>
       </c>
       <c r="I64" t="s">
-        <v>295</v>
+        <v>211</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -2824,28 +2527,28 @@
         <v>72</v>
       </c>
       <c r="B65">
-        <v>1004.02</v>
+        <v>1192</v>
       </c>
       <c r="C65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D65">
-        <v>45.5</v>
+        <v>67.5</v>
       </c>
       <c r="E65" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="F65" t="s">
-        <v>184</v>
+        <v>141</v>
       </c>
       <c r="G65" t="s">
-        <v>226</v>
+        <v>166</v>
       </c>
       <c r="H65" t="s">
-        <v>263</v>
+        <v>191</v>
       </c>
       <c r="I65" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -2853,28 +2556,28 @@
         <v>73</v>
       </c>
       <c r="B66">
-        <v>1001.4</v>
+        <v>1191.07</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D66">
-        <v>46.9</v>
+        <v>53.3</v>
       </c>
       <c r="E66" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="F66" t="s">
-        <v>185</v>
+        <v>142</v>
       </c>
       <c r="G66" t="s">
-        <v>227</v>
+        <v>167</v>
       </c>
       <c r="H66" t="s">
-        <v>264</v>
+        <v>192</v>
       </c>
       <c r="I66" t="s">
-        <v>296</v>
+        <v>172</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -2882,28 +2585,25 @@
         <v>74</v>
       </c>
       <c r="B67">
-        <v>991.1</v>
+        <v>1183.2</v>
       </c>
       <c r="C67">
         <v>1</v>
       </c>
       <c r="D67">
-        <v>66.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E67" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="F67" t="s">
-        <v>186</v>
-      </c>
-      <c r="G67" t="s">
-        <v>228</v>
+        <v>143</v>
       </c>
       <c r="H67" t="s">
-        <v>265</v>
+        <v>172</v>
       </c>
       <c r="I67" t="s">
-        <v>239</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -2911,28 +2611,19 @@
         <v>75</v>
       </c>
       <c r="B68">
-        <v>984.1</v>
+        <v>1174.8</v>
       </c>
       <c r="C68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D68">
-        <v>50</v>
-      </c>
-      <c r="E68" t="s">
-        <v>141</v>
-      </c>
-      <c r="F68" t="s">
-        <v>187</v>
-      </c>
-      <c r="G68" t="s">
-        <v>229</v>
+        <v>68.5</v>
       </c>
       <c r="H68" t="s">
-        <v>266</v>
+        <v>172</v>
       </c>
       <c r="I68" t="s">
-        <v>297</v>
+        <v>172</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -2940,19 +2631,28 @@
         <v>76</v>
       </c>
       <c r="B69">
-        <v>963.6</v>
+        <v>1174.2</v>
       </c>
       <c r="C69">
         <v>1</v>
       </c>
       <c r="D69">
-        <v>56.3</v>
+        <v>75</v>
+      </c>
+      <c r="E69" t="s">
+        <v>113</v>
+      </c>
+      <c r="F69" t="s">
+        <v>144</v>
+      </c>
+      <c r="G69" t="s">
+        <v>168</v>
       </c>
       <c r="H69" t="s">
-        <v>239</v>
+        <v>193</v>
       </c>
       <c r="I69" t="s">
-        <v>239</v>
+        <v>213</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -2960,28 +2660,28 @@
         <v>77</v>
       </c>
       <c r="B70">
-        <v>960.7</v>
+        <v>1163.7</v>
       </c>
       <c r="C70">
         <v>1</v>
       </c>
       <c r="D70">
-        <v>27.1</v>
+        <v>55</v>
       </c>
       <c r="E70" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="F70" t="s">
-        <v>188</v>
+        <v>145</v>
       </c>
       <c r="G70" t="s">
-        <v>213</v>
+        <v>169</v>
       </c>
       <c r="H70" t="s">
-        <v>267</v>
+        <v>194</v>
       </c>
       <c r="I70" t="s">
-        <v>239</v>
+        <v>214</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -2989,28 +2689,19 @@
         <v>78</v>
       </c>
       <c r="B71">
-        <v>955.9</v>
+        <v>1162.5</v>
       </c>
       <c r="C71">
         <v>1</v>
       </c>
       <c r="D71">
-        <v>68.7</v>
-      </c>
-      <c r="E71" t="s">
-        <v>143</v>
-      </c>
-      <c r="F71" t="s">
-        <v>189</v>
-      </c>
-      <c r="G71" t="s">
-        <v>230</v>
+        <v>73.3</v>
       </c>
       <c r="H71" t="s">
-        <v>268</v>
+        <v>172</v>
       </c>
       <c r="I71" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -3018,28 +2709,28 @@
         <v>79</v>
       </c>
       <c r="B72">
-        <v>955</v>
+        <v>1153.6</v>
       </c>
       <c r="C72">
         <v>1</v>
       </c>
       <c r="D72">
-        <v>65.40000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="E72" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="F72" t="s">
-        <v>190</v>
+        <v>146</v>
       </c>
       <c r="G72" t="s">
-        <v>231</v>
+        <v>170</v>
       </c>
       <c r="H72" t="s">
-        <v>269</v>
+        <v>195</v>
       </c>
       <c r="I72" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -3047,19 +2738,28 @@
         <v>80</v>
       </c>
       <c r="B73">
-        <v>949.8</v>
+        <v>1150.4</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D73">
-        <v>45.8</v>
+        <v>36.1</v>
+      </c>
+      <c r="E73" t="s">
+        <v>116</v>
+      </c>
+      <c r="F73" t="s">
+        <v>147</v>
+      </c>
+      <c r="G73" t="s">
+        <v>171</v>
       </c>
       <c r="H73" t="s">
-        <v>239</v>
+        <v>196</v>
       </c>
       <c r="I73" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -3067,28 +2767,19 @@
         <v>81</v>
       </c>
       <c r="B74">
-        <v>949.1</v>
+        <v>1148.7</v>
       </c>
       <c r="C74">
         <v>1</v>
       </c>
       <c r="D74">
-        <v>55.9</v>
-      </c>
-      <c r="E74" t="s">
-        <v>145</v>
-      </c>
-      <c r="F74" t="s">
-        <v>191</v>
-      </c>
-      <c r="G74" t="s">
-        <v>232</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H74" t="s">
-        <v>270</v>
+        <v>172</v>
       </c>
       <c r="I74" t="s">
-        <v>298</v>
+        <v>172</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -3096,19 +2787,19 @@
         <v>82</v>
       </c>
       <c r="B75">
-        <v>948.8</v>
+        <v>1144.1</v>
       </c>
       <c r="C75">
         <v>1</v>
       </c>
       <c r="D75">
-        <v>52.6</v>
+        <v>59.6</v>
       </c>
       <c r="H75" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I75" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -3116,19 +2807,19 @@
         <v>83</v>
       </c>
       <c r="B76">
-        <v>934.7</v>
+        <v>1141.8</v>
       </c>
       <c r="C76">
         <v>1</v>
       </c>
       <c r="D76">
-        <v>9.9</v>
+        <v>44.6</v>
       </c>
       <c r="H76" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I76" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -3136,19 +2827,19 @@
         <v>84</v>
       </c>
       <c r="B77">
-        <v>931</v>
+        <v>1127.4</v>
       </c>
       <c r="C77">
         <v>1</v>
       </c>
       <c r="D77">
-        <v>47.6</v>
+        <v>69.5</v>
       </c>
       <c r="H77" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I77" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -3156,612 +2847,19 @@
         <v>85</v>
       </c>
       <c r="B78">
-        <v>924.1</v>
+        <v>1121.8</v>
       </c>
       <c r="C78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D78">
-        <v>45.8</v>
+        <v>64.7</v>
       </c>
       <c r="H78" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="I78" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9">
-      <c r="A79" t="s">
-        <v>86</v>
-      </c>
-      <c r="B79">
-        <v>921.3</v>
-      </c>
-      <c r="C79">
-        <v>1</v>
-      </c>
-      <c r="D79">
-        <v>61.2</v>
-      </c>
-      <c r="H79" t="s">
-        <v>239</v>
-      </c>
-      <c r="I79" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9">
-      <c r="A80" t="s">
-        <v>87</v>
-      </c>
-      <c r="B80">
-        <v>920.8</v>
-      </c>
-      <c r="C80">
-        <v>2</v>
-      </c>
-      <c r="D80">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="E80" t="s">
-        <v>146</v>
-      </c>
-      <c r="F80" t="s">
-        <v>192</v>
-      </c>
-      <c r="G80" t="s">
-        <v>233</v>
-      </c>
-      <c r="H80" t="s">
-        <v>271</v>
-      </c>
-      <c r="I80" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9">
-      <c r="A81" t="s">
-        <v>88</v>
-      </c>
-      <c r="B81">
-        <v>907.6</v>
-      </c>
-      <c r="C81">
-        <v>1</v>
-      </c>
-      <c r="D81">
-        <v>27.1</v>
-      </c>
-      <c r="E81" t="s">
-        <v>147</v>
-      </c>
-      <c r="F81" t="s">
-        <v>193</v>
-      </c>
-      <c r="G81" t="s">
-        <v>213</v>
-      </c>
-      <c r="H81" t="s">
-        <v>272</v>
-      </c>
-      <c r="I81" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9">
-      <c r="A82" t="s">
-        <v>89</v>
-      </c>
-      <c r="B82">
-        <v>907</v>
-      </c>
-      <c r="C82">
-        <v>1</v>
-      </c>
-      <c r="D82">
-        <v>34.1</v>
-      </c>
-      <c r="H82" t="s">
-        <v>239</v>
-      </c>
-      <c r="I82" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9">
-      <c r="A83" t="s">
-        <v>90</v>
-      </c>
-      <c r="B83">
-        <v>880.3</v>
-      </c>
-      <c r="C83">
-        <v>1</v>
-      </c>
-      <c r="D83">
-        <v>57.3</v>
-      </c>
-      <c r="E83" t="s">
-        <v>148</v>
-      </c>
-      <c r="F83" t="s">
-        <v>194</v>
-      </c>
-      <c r="G83" t="s">
-        <v>234</v>
-      </c>
-      <c r="H83" t="s">
-        <v>273</v>
-      </c>
-      <c r="I83" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9">
-      <c r="A84" t="s">
-        <v>91</v>
-      </c>
-      <c r="B84">
-        <v>879.6</v>
-      </c>
-      <c r="C84">
-        <v>1</v>
-      </c>
-      <c r="D84">
-        <v>58.4</v>
-      </c>
-      <c r="H84" t="s">
-        <v>239</v>
-      </c>
-      <c r="I84" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9">
-      <c r="A85" t="s">
-        <v>92</v>
-      </c>
-      <c r="B85">
-        <v>874</v>
-      </c>
-      <c r="C85">
-        <v>2</v>
-      </c>
-      <c r="D85">
-        <v>63</v>
-      </c>
-      <c r="H85" t="s">
-        <v>239</v>
-      </c>
-      <c r="I85" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9">
-      <c r="A86" t="s">
-        <v>93</v>
-      </c>
-      <c r="B86">
-        <v>871.3</v>
-      </c>
-      <c r="C86">
-        <v>3</v>
-      </c>
-      <c r="D86">
-        <v>29.9</v>
-      </c>
-      <c r="E86" t="s">
-        <v>149</v>
-      </c>
-      <c r="F86" t="s">
-        <v>195</v>
-      </c>
-      <c r="G86" t="s">
-        <v>209</v>
-      </c>
-      <c r="H86" t="s">
-        <v>274</v>
-      </c>
-      <c r="I86" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9">
-      <c r="A87" t="s">
-        <v>94</v>
-      </c>
-      <c r="B87">
-        <v>870.8</v>
-      </c>
-      <c r="C87">
-        <v>1</v>
-      </c>
-      <c r="D87">
-        <v>26.9</v>
-      </c>
-      <c r="H87" t="s">
-        <v>239</v>
-      </c>
-      <c r="I87" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9">
-      <c r="A88" t="s">
-        <v>95</v>
-      </c>
-      <c r="B88">
-        <v>865.8</v>
-      </c>
-      <c r="C88">
-        <v>1</v>
-      </c>
-      <c r="D88">
-        <v>57.1</v>
-      </c>
-      <c r="H88" t="s">
-        <v>239</v>
-      </c>
-      <c r="I88" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9">
-      <c r="A89" t="s">
-        <v>96</v>
-      </c>
-      <c r="B89">
-        <v>864</v>
-      </c>
-      <c r="C89">
-        <v>1</v>
-      </c>
-      <c r="D89">
-        <v>54.6</v>
-      </c>
-      <c r="E89" t="s">
-        <v>150</v>
-      </c>
-      <c r="F89" t="s">
-        <v>196</v>
-      </c>
-      <c r="H89" t="s">
-        <v>239</v>
-      </c>
-      <c r="I89" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9">
-      <c r="A90" t="s">
-        <v>97</v>
-      </c>
-      <c r="B90">
-        <v>860.7</v>
-      </c>
-      <c r="C90">
-        <v>1</v>
-      </c>
-      <c r="D90">
-        <v>29.9</v>
-      </c>
-      <c r="E90" t="s">
-        <v>151</v>
-      </c>
-      <c r="F90" t="s">
-        <v>197</v>
-      </c>
-      <c r="G90" t="s">
-        <v>209</v>
-      </c>
-      <c r="H90" t="s">
-        <v>275</v>
-      </c>
-      <c r="I90" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9">
-      <c r="A91" t="s">
-        <v>98</v>
-      </c>
-      <c r="B91">
-        <v>856.89</v>
-      </c>
-      <c r="C91">
-        <v>1</v>
-      </c>
-      <c r="D91">
-        <v>65.5</v>
-      </c>
-      <c r="H91" t="s">
-        <v>239</v>
-      </c>
-      <c r="I91" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9">
-      <c r="A92" t="s">
-        <v>99</v>
-      </c>
-      <c r="B92">
-        <v>854.1</v>
-      </c>
-      <c r="C92">
-        <v>1</v>
-      </c>
-      <c r="D92">
-        <v>29.3</v>
-      </c>
-      <c r="H92" t="s">
-        <v>239</v>
-      </c>
-      <c r="I92" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9">
-      <c r="A93" t="s">
-        <v>100</v>
-      </c>
-      <c r="B93">
-        <v>852</v>
-      </c>
-      <c r="C93">
-        <v>1</v>
-      </c>
-      <c r="D93">
-        <v>45.7</v>
-      </c>
-      <c r="E93" t="s">
-        <v>152</v>
-      </c>
-      <c r="F93" t="s">
-        <v>198</v>
-      </c>
-      <c r="G93" t="s">
-        <v>235</v>
-      </c>
-      <c r="H93" t="s">
-        <v>276</v>
-      </c>
-      <c r="I93" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9">
-      <c r="A94" t="s">
-        <v>101</v>
-      </c>
-      <c r="B94">
-        <v>833.3</v>
-      </c>
-      <c r="C94">
-        <v>1</v>
-      </c>
-      <c r="D94">
-        <v>21.6</v>
-      </c>
-      <c r="H94" t="s">
-        <v>239</v>
-      </c>
-      <c r="I94" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9">
-      <c r="A95" t="s">
-        <v>102</v>
-      </c>
-      <c r="B95">
-        <v>827.6</v>
-      </c>
-      <c r="C95">
-        <v>1</v>
-      </c>
-      <c r="D95">
-        <v>39.7</v>
-      </c>
-      <c r="H95" t="s">
-        <v>239</v>
-      </c>
-      <c r="I95" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9">
-      <c r="A96" t="s">
-        <v>103</v>
-      </c>
-      <c r="B96">
-        <v>827</v>
-      </c>
-      <c r="C96">
-        <v>1</v>
-      </c>
-      <c r="D96">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="E96" t="s">
-        <v>153</v>
-      </c>
-      <c r="F96" t="s">
-        <v>199</v>
-      </c>
-      <c r="G96" t="s">
-        <v>236</v>
-      </c>
-      <c r="H96" t="s">
-        <v>277</v>
-      </c>
-      <c r="I96" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9">
-      <c r="A97" t="s">
-        <v>104</v>
-      </c>
-      <c r="B97">
-        <v>823</v>
-      </c>
-      <c r="C97">
-        <v>1</v>
-      </c>
-      <c r="D97">
-        <v>59.5</v>
-      </c>
-      <c r="H97" t="s">
-        <v>239</v>
-      </c>
-      <c r="I97" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9">
-      <c r="A98" t="s">
-        <v>105</v>
-      </c>
-      <c r="B98">
-        <v>821</v>
-      </c>
-      <c r="C98">
-        <v>2</v>
-      </c>
-      <c r="D98">
-        <v>42.6</v>
-      </c>
-      <c r="E98" t="s">
-        <v>154</v>
-      </c>
-      <c r="F98" t="s">
-        <v>200</v>
-      </c>
-      <c r="G98" t="s">
-        <v>237</v>
-      </c>
-      <c r="H98" t="s">
-        <v>278</v>
-      </c>
-      <c r="I98" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9">
-      <c r="A99" t="s">
-        <v>106</v>
-      </c>
-      <c r="B99">
-        <v>819</v>
-      </c>
-      <c r="C99">
-        <v>1</v>
-      </c>
-      <c r="D99">
-        <v>54.2</v>
-      </c>
-      <c r="H99" t="s">
-        <v>239</v>
-      </c>
-      <c r="I99" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9">
-      <c r="A100" t="s">
-        <v>107</v>
-      </c>
-      <c r="B100">
-        <v>817</v>
-      </c>
-      <c r="C100">
-        <v>1</v>
-      </c>
-      <c r="D100">
-        <v>61.2</v>
-      </c>
-      <c r="E100" t="s">
-        <v>155</v>
-      </c>
-      <c r="F100" t="s">
-        <v>201</v>
-      </c>
-      <c r="G100" t="s">
-        <v>238</v>
-      </c>
-      <c r="H100" t="s">
-        <v>279</v>
-      </c>
-      <c r="I100" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9">
-      <c r="A101" t="s">
-        <v>108</v>
-      </c>
-      <c r="B101">
-        <v>810.7</v>
-      </c>
-      <c r="C101">
-        <v>1</v>
-      </c>
-      <c r="D101">
-        <v>12.2</v>
-      </c>
-      <c r="H101" t="s">
-        <v>239</v>
-      </c>
-      <c r="I101" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9">
-      <c r="A102" t="s">
-        <v>109</v>
-      </c>
-      <c r="B102">
-        <v>806.2</v>
-      </c>
-      <c r="C102">
-        <v>1</v>
-      </c>
-      <c r="D102">
-        <v>25.7</v>
-      </c>
-      <c r="E102" t="s">
-        <v>156</v>
-      </c>
-      <c r="F102" t="s">
-        <v>202</v>
-      </c>
-      <c r="H102" t="s">
-        <v>239</v>
-      </c>
-      <c r="I102" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9">
-      <c r="A103" t="s">
-        <v>110</v>
-      </c>
-      <c r="B103">
-        <v>803.5</v>
-      </c>
-      <c r="C103">
-        <v>1</v>
-      </c>
-      <c r="D103">
-        <v>59.8</v>
-      </c>
-      <c r="H103" t="s">
-        <v>239</v>
-      </c>
-      <c r="I103" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -3776,16 +2874,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>304</v>
+        <v>216</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>305</v>
+        <v>217</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>306</v>
+        <v>218</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>307</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -3793,13 +2891,13 @@
         <v>200000</v>
       </c>
       <c r="B2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="C2">
-        <v>200398.465</v>
+        <v>200370.455</v>
       </c>
       <c r="D2">
-        <v>125</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
